--- a/research/traditional_assets/database/data/brazil/brazil_building_materials.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_building_materials.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1164353418001956</v>
+        <v>0.116069161638075</v>
       </c>
       <c r="C2">
-        <v>324.12663850726</v>
+        <v>321.7236885236599</v>
       </c>
       <c r="D2">
-        <v>290.92663850726</v>
+        <v>292.4426885236599</v>
       </c>
       <c r="E2">
-        <v>-308.5</v>
+        <v>-304.581</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.919</v>
       </c>
       <c r="G2">
         <v>33.2</v>
@@ -1445,28 +1445,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1971257</v>
       </c>
       <c r="N2">
-        <v>45.36666666666667</v>
+        <v>45.16954096666667</v>
       </c>
       <c r="O2">
-        <v>15.42466666666667</v>
+        <v>15.35764392866667</v>
       </c>
       <c r="P2">
-        <v>29.942</v>
+        <v>29.81189703800001</v>
       </c>
       <c r="Q2">
-        <v>34.242</v>
+        <v>34.11189703800001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1164353418001956</v>
+        <v>0.1169062440788636</v>
       </c>
       <c r="T2">
-        <v>0.9206152946161339</v>
+        <v>0.9267527299135747</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>230.1408018673703</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.116069161638075</v>
+        <v>0.1157029814759543</v>
       </c>
       <c r="C3">
-        <v>321.7236885236599</v>
+        <v>319.3366219095261</v>
       </c>
       <c r="D3">
-        <v>292.4426885236599</v>
+        <v>293.9746219095261</v>
       </c>
       <c r="E3">
-        <v>-304.581</v>
+        <v>-300.662</v>
       </c>
       <c r="F3">
-        <v>3.919</v>
+        <v>7.838</v>
       </c>
       <c r="G3">
         <v>33.2</v>
@@ -1527,28 +1527,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M3">
-        <v>0.1971257</v>
+        <v>0.3942514</v>
       </c>
       <c r="N3">
-        <v>45.16954096666667</v>
+        <v>44.97241526666667</v>
       </c>
       <c r="O3">
-        <v>15.35764392866667</v>
+        <v>15.29062119066667</v>
       </c>
       <c r="P3">
-        <v>29.81189703800001</v>
+        <v>29.681794076</v>
       </c>
       <c r="Q3">
-        <v>34.11189703800001</v>
+        <v>33.981794076</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1169062440788636</v>
+        <v>0.1173867566081166</v>
       </c>
       <c r="T3">
-        <v>0.9267527299135747</v>
+        <v>0.9330154189925961</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>230.1408018673703</v>
+        <v>115.0704009336851</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1157029814759543</v>
+        <v>0.1153368013138336</v>
       </c>
       <c r="C4">
-        <v>319.3366219095261</v>
+        <v>316.9656895898951</v>
       </c>
       <c r="D4">
-        <v>293.9746219095261</v>
+        <v>295.5226895898952</v>
       </c>
       <c r="E4">
-        <v>-300.662</v>
+        <v>-296.743</v>
       </c>
       <c r="F4">
-        <v>7.838</v>
+        <v>11.757</v>
       </c>
       <c r="G4">
         <v>33.2</v>
@@ -1609,28 +1609,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M4">
-        <v>0.3942514</v>
+        <v>0.5913771</v>
       </c>
       <c r="N4">
-        <v>44.97241526666667</v>
+        <v>44.77528956666667</v>
       </c>
       <c r="O4">
-        <v>15.29062119066667</v>
+        <v>15.22359845266667</v>
       </c>
       <c r="P4">
-        <v>29.681794076</v>
+        <v>29.551691114</v>
       </c>
       <c r="Q4">
-        <v>33.981794076</v>
+        <v>33.851691114</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1173867566081166</v>
+        <v>0.1178771766121996</v>
       </c>
       <c r="T4">
-        <v>0.9330154189925961</v>
+        <v>0.9394072356814942</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>115.0704009336851</v>
+        <v>76.71360062245675</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1153368013138336</v>
+        <v>0.114970621151713</v>
       </c>
       <c r="C5">
-        <v>316.9656895898951</v>
+        <v>314.6111478032602</v>
       </c>
       <c r="D5">
-        <v>295.5226895898952</v>
+        <v>297.0871478032602</v>
       </c>
       <c r="E5">
-        <v>-296.743</v>
+        <v>-292.824</v>
       </c>
       <c r="F5">
-        <v>11.757</v>
+        <v>15.676</v>
       </c>
       <c r="G5">
         <v>33.2</v>
@@ -1691,28 +1691,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M5">
-        <v>0.5913771</v>
+        <v>0.7885027999999999</v>
       </c>
       <c r="N5">
-        <v>44.77528956666667</v>
+        <v>44.57816386666667</v>
       </c>
       <c r="O5">
-        <v>15.22359845266667</v>
+        <v>15.15657571466667</v>
       </c>
       <c r="P5">
-        <v>29.551691114</v>
+        <v>29.421588152</v>
       </c>
       <c r="Q5">
-        <v>33.851691114</v>
+        <v>33.721588152</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1178771766121996</v>
+        <v>0.118377813699701</v>
       </c>
       <c r="T5">
-        <v>0.9394072356814942</v>
+        <v>0.9459322152180777</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.71360062245675</v>
+        <v>57.53520046684257</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.114970621151713</v>
+        <v>0.1146044409895923</v>
       </c>
       <c r="C6">
-        <v>314.6111478032602</v>
+        <v>312.273258242963</v>
       </c>
       <c r="D6">
-        <v>297.0871478032602</v>
+        <v>298.6682582429631</v>
       </c>
       <c r="E6">
-        <v>-292.824</v>
+        <v>-288.905</v>
       </c>
       <c r="F6">
-        <v>15.676</v>
+        <v>19.595</v>
       </c>
       <c r="G6">
         <v>33.2</v>
@@ -1773,28 +1773,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M6">
-        <v>0.7885027999999999</v>
+        <v>0.9856284999999999</v>
       </c>
       <c r="N6">
-        <v>44.57816386666667</v>
+        <v>44.38103816666668</v>
       </c>
       <c r="O6">
-        <v>15.15657571466667</v>
+        <v>15.08955297666667</v>
       </c>
       <c r="P6">
-        <v>29.421588152</v>
+        <v>29.29148519000001</v>
       </c>
       <c r="Q6">
-        <v>33.721588152</v>
+        <v>33.59148519000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.118377813699701</v>
+        <v>0.1188889905153603</v>
       </c>
       <c r="T6">
-        <v>0.9459322152180777</v>
+        <v>0.9525945627449048</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.53520046684257</v>
+        <v>46.02816037347407</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1146044409895923</v>
+        <v>0.1142382608274716</v>
       </c>
       <c r="C7">
-        <v>312.273258242963</v>
+        <v>309.9522882031254</v>
       </c>
       <c r="D7">
-        <v>298.6682582429631</v>
+        <v>300.2662882031254</v>
       </c>
       <c r="E7">
-        <v>-288.905</v>
+        <v>-284.986</v>
       </c>
       <c r="F7">
-        <v>19.595</v>
+        <v>23.514</v>
       </c>
       <c r="G7">
         <v>33.2</v>
@@ -1855,28 +1855,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M7">
-        <v>0.9856284999999999</v>
+        <v>1.1827542</v>
       </c>
       <c r="N7">
-        <v>44.38103816666668</v>
+        <v>44.18391246666668</v>
       </c>
       <c r="O7">
-        <v>15.08955297666667</v>
+        <v>15.02253023866667</v>
       </c>
       <c r="P7">
-        <v>29.29148519000001</v>
+        <v>29.16138222800001</v>
       </c>
       <c r="Q7">
-        <v>33.59148519000001</v>
+        <v>33.46138222800001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1188889905153603</v>
+        <v>0.1194110434334805</v>
       </c>
       <c r="T7">
-        <v>0.9525945627449048</v>
+        <v>0.9593986623467711</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.02816037347407</v>
+        <v>38.35680031122838</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1142382608274716</v>
+        <v>0.113872080665351</v>
       </c>
       <c r="C8">
-        <v>309.9522882031254</v>
+        <v>307.6485107292904</v>
       </c>
       <c r="D8">
-        <v>300.2662882031254</v>
+        <v>301.8815107292904</v>
       </c>
       <c r="E8">
-        <v>-284.986</v>
+        <v>-281.067</v>
       </c>
       <c r="F8">
-        <v>23.514</v>
+        <v>27.433</v>
       </c>
       <c r="G8">
         <v>33.2</v>
@@ -1937,28 +1937,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M8">
-        <v>1.1827542</v>
+        <v>1.3798799</v>
       </c>
       <c r="N8">
-        <v>44.18391246666668</v>
+        <v>43.98678676666668</v>
       </c>
       <c r="O8">
-        <v>15.02253023866667</v>
+        <v>14.95550750066667</v>
       </c>
       <c r="P8">
-        <v>29.16138222800001</v>
+        <v>29.03127926600001</v>
       </c>
       <c r="Q8">
-        <v>33.46138222800001</v>
+        <v>33.33127926600001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1194110434334805</v>
+        <v>0.1199443232960763</v>
       </c>
       <c r="T8">
-        <v>0.9593986623467711</v>
+        <v>0.9663490866712579</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.35680031122838</v>
+        <v>32.87725740962433</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.113872080665351</v>
+        <v>0.1135059005032303</v>
       </c>
       <c r="C9">
-        <v>307.6485107292904</v>
+        <v>305.3622047739521</v>
       </c>
       <c r="D9">
-        <v>301.8815107292904</v>
+        <v>303.5142047739521</v>
       </c>
       <c r="E9">
-        <v>-281.067</v>
+        <v>-277.148</v>
       </c>
       <c r="F9">
-        <v>27.433</v>
+        <v>31.352</v>
       </c>
       <c r="G9">
         <v>33.2</v>
@@ -2019,28 +2019,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M9">
-        <v>1.3798799</v>
+        <v>1.5770056</v>
       </c>
       <c r="N9">
-        <v>43.98678676666668</v>
+        <v>43.78966106666667</v>
       </c>
       <c r="O9">
-        <v>14.95550750066667</v>
+        <v>14.88848476266667</v>
       </c>
       <c r="P9">
-        <v>29.03127926600001</v>
+        <v>28.901176304</v>
       </c>
       <c r="Q9">
-        <v>33.33127926600001</v>
+        <v>33.201176304</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1199443232960763</v>
+        <v>0.1204891961991634</v>
       </c>
       <c r="T9">
-        <v>0.9663490866712581</v>
+        <v>0.9734506071767119</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.87725740962433</v>
+        <v>28.76760023342129</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1135059005032303</v>
+        <v>0.1131397203411097</v>
       </c>
       <c r="C10">
-        <v>305.3622047739521</v>
+        <v>303.09365535716</v>
       </c>
       <c r="D10">
-        <v>303.5142047739521</v>
+        <v>305.16465535716</v>
       </c>
       <c r="E10">
-        <v>-277.148</v>
+        <v>-273.229</v>
       </c>
       <c r="F10">
-        <v>31.352</v>
+        <v>35.27099999999999</v>
       </c>
       <c r="G10">
         <v>33.2</v>
@@ -2101,28 +2101,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M10">
-        <v>1.5770056</v>
+        <v>1.7741313</v>
       </c>
       <c r="N10">
-        <v>43.78966106666667</v>
+        <v>43.59253536666667</v>
       </c>
       <c r="O10">
-        <v>14.88848476266667</v>
+        <v>14.82146202466667</v>
       </c>
       <c r="P10">
-        <v>28.901176304</v>
+        <v>28.771073342</v>
       </c>
       <c r="Q10">
-        <v>33.201176304</v>
+        <v>33.07107334200001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1204891961991634</v>
+        <v>0.1210460443308897</v>
       </c>
       <c r="T10">
-        <v>0.9734506071767119</v>
+        <v>0.9807082050559123</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.76760023342129</v>
+        <v>25.57120020748559</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1131397203411097</v>
+        <v>0.112773540178989</v>
       </c>
       <c r="C11">
-        <v>303.09365535716</v>
+        <v>300.8431537323921</v>
       </c>
       <c r="D11">
-        <v>305.16465535716</v>
+        <v>306.8331537323921</v>
       </c>
       <c r="E11">
-        <v>-273.229</v>
+        <v>-269.31</v>
       </c>
       <c r="F11">
-        <v>35.27099999999999</v>
+        <v>39.19</v>
       </c>
       <c r="G11">
         <v>33.2</v>
@@ -2183,28 +2183,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M11">
-        <v>1.7741313</v>
+        <v>1.971257</v>
       </c>
       <c r="N11">
-        <v>43.59253536666667</v>
+        <v>43.39540966666667</v>
       </c>
       <c r="O11">
-        <v>14.82146202466667</v>
+        <v>14.75443928666667</v>
       </c>
       <c r="P11">
-        <v>28.771073342</v>
+        <v>28.64097038</v>
       </c>
       <c r="Q11">
-        <v>33.07107334200001</v>
+        <v>32.94097038</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1210460443308897</v>
+        <v>0.1216152668655433</v>
       </c>
       <c r="T11">
-        <v>0.9807082050559123</v>
+        <v>0.9881270828879837</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.57120020748559</v>
+        <v>23.01408018673703</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.112773540178989</v>
+        <v>0.1124073600168683</v>
       </c>
       <c r="C12">
-        <v>300.8431537323921</v>
+        <v>298.6109975578984</v>
       </c>
       <c r="D12">
-        <v>306.8331537323921</v>
+        <v>308.5199975578984</v>
       </c>
       <c r="E12">
-        <v>-269.31</v>
+        <v>-265.391</v>
       </c>
       <c r="F12">
-        <v>39.19</v>
+        <v>43.10899999999999</v>
       </c>
       <c r="G12">
         <v>33.2</v>
@@ -2265,28 +2265,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M12">
-        <v>1.971257</v>
+        <v>2.1683827</v>
       </c>
       <c r="N12">
-        <v>43.39540966666667</v>
+        <v>43.19828396666667</v>
       </c>
       <c r="O12">
-        <v>14.75443928666667</v>
+        <v>14.68741654866667</v>
       </c>
       <c r="P12">
-        <v>28.64097038</v>
+        <v>28.510867418</v>
       </c>
       <c r="Q12">
-        <v>32.94097038</v>
+        <v>32.810867418</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1216152668655433</v>
+        <v>0.1221972809178296</v>
       </c>
       <c r="T12">
-        <v>0.9881270828879837</v>
+        <v>0.9957126770758319</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.01408018673703</v>
+        <v>20.92189107885185</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1124073600168683</v>
+        <v>0.1120411798547477</v>
       </c>
       <c r="C13">
-        <v>298.6109975578984</v>
+        <v>296.3974910737285</v>
       </c>
       <c r="D13">
-        <v>308.5199975578984</v>
+        <v>310.2254910737286</v>
       </c>
       <c r="E13">
-        <v>-265.391</v>
+        <v>-261.472</v>
       </c>
       <c r="F13">
-        <v>43.10899999999999</v>
+        <v>47.028</v>
       </c>
       <c r="G13">
         <v>33.2</v>
@@ -2347,28 +2347,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M13">
-        <v>2.1683827</v>
+        <v>2.3655084</v>
       </c>
       <c r="N13">
-        <v>43.19828396666667</v>
+        <v>43.00115826666667</v>
       </c>
       <c r="O13">
-        <v>14.68741654866667</v>
+        <v>14.62039381066667</v>
       </c>
       <c r="P13">
-        <v>28.510867418</v>
+        <v>28.380764456</v>
       </c>
       <c r="Q13">
-        <v>32.810867418</v>
+        <v>32.68076445600001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1221972809178296</v>
+        <v>0.1227925225622132</v>
       </c>
       <c r="T13">
-        <v>0.9957126770758319</v>
+        <v>1.003470671131586</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.92189107885185</v>
+        <v>19.17840015561419</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1120411798547477</v>
+        <v>0.111674999692627</v>
       </c>
       <c r="C14">
-        <v>296.3974910737285</v>
+        <v>294.2029452846643</v>
       </c>
       <c r="D14">
-        <v>310.2254910737286</v>
+        <v>311.9499452846643</v>
       </c>
       <c r="E14">
-        <v>-261.472</v>
+        <v>-257.553</v>
       </c>
       <c r="F14">
-        <v>47.028</v>
+        <v>50.947</v>
       </c>
       <c r="G14">
         <v>33.2</v>
@@ -2429,28 +2429,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M14">
-        <v>2.3655084</v>
+        <v>2.562634099999999</v>
       </c>
       <c r="N14">
-        <v>43.00115826666667</v>
+        <v>42.80403256666668</v>
       </c>
       <c r="O14">
-        <v>14.62039381066667</v>
+        <v>14.55337107266667</v>
       </c>
       <c r="P14">
-        <v>28.380764456</v>
+        <v>28.25066149400001</v>
       </c>
       <c r="Q14">
-        <v>32.68076445600001</v>
+        <v>32.55066149400001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1227925225622132</v>
+        <v>0.1234014479225597</v>
       </c>
       <c r="T14">
-        <v>1.003470671131586</v>
+        <v>1.011407009878277</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.17840015561419</v>
+        <v>17.70313860518234</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.111674999692627</v>
+        <v>0.1113088195305063</v>
       </c>
       <c r="C15">
-        <v>294.2029452846643</v>
+        <v>292.0276781492855</v>
       </c>
       <c r="D15">
-        <v>311.9499452846643</v>
+        <v>313.6936781492855</v>
       </c>
       <c r="E15">
-        <v>-257.553</v>
+        <v>-253.634</v>
       </c>
       <c r="F15">
-        <v>50.947</v>
+        <v>54.866</v>
       </c>
       <c r="G15">
         <v>33.2</v>
@@ -2511,28 +2511,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M15">
-        <v>2.562634099999999</v>
+        <v>2.7597598</v>
       </c>
       <c r="N15">
-        <v>42.80403256666668</v>
+        <v>42.60690686666668</v>
       </c>
       <c r="O15">
-        <v>14.55337107266667</v>
+        <v>14.48634833466667</v>
       </c>
       <c r="P15">
-        <v>28.25066149400001</v>
+        <v>28.120558532</v>
       </c>
       <c r="Q15">
-        <v>32.55066149400001</v>
+        <v>32.420558532</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1234014479225597</v>
+        <v>0.124024534337798</v>
       </c>
       <c r="T15">
-        <v>1.011407009878277</v>
+        <v>1.019527914642332</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.70313860518234</v>
+        <v>16.43862870481216</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1113088195305063</v>
+        <v>0.1109426393683857</v>
       </c>
       <c r="C16">
-        <v>292.0276781492855</v>
+        <v>289.8720147754135</v>
       </c>
       <c r="D16">
-        <v>313.6936781492855</v>
+        <v>315.4570147754135</v>
       </c>
       <c r="E16">
-        <v>-253.634</v>
+        <v>-249.715</v>
       </c>
       <c r="F16">
-        <v>54.866</v>
+        <v>58.785</v>
       </c>
       <c r="G16">
         <v>33.2</v>
@@ -2593,28 +2593,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M16">
-        <v>2.7597598</v>
+        <v>2.9568855</v>
       </c>
       <c r="N16">
-        <v>42.60690686666668</v>
+        <v>42.40978116666668</v>
       </c>
       <c r="O16">
-        <v>14.48634833466667</v>
+        <v>14.41932559666667</v>
       </c>
       <c r="P16">
-        <v>28.120558532</v>
+        <v>27.99045557000001</v>
       </c>
       <c r="Q16">
-        <v>32.420558532</v>
+        <v>32.29045557000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.124024534337798</v>
+        <v>0.1246622816098655</v>
       </c>
       <c r="T16">
-        <v>1.019527914642332</v>
+        <v>1.027839899518484</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.43862870481216</v>
+        <v>15.34272012449135</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1109426393683857</v>
+        <v>0.110576459206265</v>
       </c>
       <c r="C17">
-        <v>289.8720147754135</v>
+        <v>287.7362876221854</v>
       </c>
       <c r="D17">
-        <v>315.4570147754135</v>
+        <v>317.2402876221855</v>
       </c>
       <c r="E17">
-        <v>-249.715</v>
+        <v>-245.796</v>
       </c>
       <c r="F17">
-        <v>58.785</v>
+        <v>62.704</v>
       </c>
       <c r="G17">
         <v>33.2</v>
@@ -2675,28 +2675,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M17">
-        <v>2.9568855</v>
+        <v>3.1540112</v>
       </c>
       <c r="N17">
-        <v>42.40978116666668</v>
+        <v>42.21265546666667</v>
       </c>
       <c r="O17">
-        <v>14.41932559666667</v>
+        <v>14.35230285866667</v>
       </c>
       <c r="P17">
-        <v>27.99045557000001</v>
+        <v>27.86035260800001</v>
       </c>
       <c r="Q17">
-        <v>32.29045557000001</v>
+        <v>32.16035260800001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1246622816098655</v>
+        <v>0.1253152133407917</v>
       </c>
       <c r="T17">
-        <v>1.027839899518484</v>
+        <v>1.036349788796448</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.34272012449135</v>
+        <v>14.38380011671064</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.110576459206265</v>
+        <v>0.1102102790441443</v>
       </c>
       <c r="C18">
-        <v>287.7362876221854</v>
+        <v>285.6208367090182</v>
       </c>
       <c r="D18">
-        <v>317.2402876221855</v>
+        <v>319.0438367090182</v>
       </c>
       <c r="E18">
-        <v>-245.796</v>
+        <v>-241.877</v>
       </c>
       <c r="F18">
-        <v>62.704</v>
+        <v>66.623</v>
       </c>
       <c r="G18">
         <v>33.2</v>
@@ -2757,28 +2757,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M18">
-        <v>3.1540112</v>
+        <v>3.3511369</v>
       </c>
       <c r="N18">
-        <v>42.21265546666667</v>
+        <v>42.01552976666667</v>
       </c>
       <c r="O18">
-        <v>14.35230285866667</v>
+        <v>14.28528012066667</v>
       </c>
       <c r="P18">
-        <v>27.86035260800001</v>
+        <v>27.730249646</v>
       </c>
       <c r="Q18">
-        <v>32.16035260800001</v>
+        <v>32.030249646</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1253152133407917</v>
+        <v>0.1259838783664389</v>
       </c>
       <c r="T18">
-        <v>1.036349788796448</v>
+        <v>1.045064735647375</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.38380011671064</v>
+        <v>13.53769422749237</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1102102790441443</v>
+        <v>0.1100222988820236</v>
       </c>
       <c r="C19">
-        <v>285.6208367090182</v>
+        <v>282.6356854374533</v>
       </c>
       <c r="D19">
-        <v>319.0438367090182</v>
+        <v>319.9776854374533</v>
       </c>
       <c r="E19">
-        <v>-241.877</v>
+        <v>-237.958</v>
       </c>
       <c r="F19">
-        <v>66.623</v>
+        <v>70.542</v>
       </c>
       <c r="G19">
         <v>33.2</v>
@@ -2839,45 +2839,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M19">
-        <v>3.3511369</v>
+        <v>3.6540756</v>
       </c>
       <c r="N19">
-        <v>42.01552976666667</v>
+        <v>41.71259106666668</v>
       </c>
       <c r="O19">
-        <v>14.28528012066667</v>
+        <v>14.18228096266667</v>
       </c>
       <c r="P19">
-        <v>27.730249646</v>
+        <v>27.53031010400001</v>
       </c>
       <c r="Q19">
-        <v>32.030249646</v>
+        <v>31.83031010400001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1259838783664389</v>
+        <v>0.1266688522951508</v>
       </c>
       <c r="T19">
-        <v>1.045064735647375</v>
+        <v>1.053992242177593</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.34</v>
       </c>
       <c r="W19">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.53769422749237</v>
+        <v>12.41536071849928</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1100222988820237</v>
+        <v>0.109666018719903</v>
       </c>
       <c r="C20">
-        <v>282.6356854374532</v>
+        <v>280.5016988753915</v>
       </c>
       <c r="D20">
-        <v>319.9776854374532</v>
+        <v>321.7626988753915</v>
       </c>
       <c r="E20">
-        <v>-237.958</v>
+        <v>-234.039</v>
       </c>
       <c r="F20">
-        <v>70.54199999999999</v>
+        <v>74.461</v>
       </c>
       <c r="G20">
         <v>33.2</v>
@@ -2921,28 +2921,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M20">
-        <v>3.654075599999999</v>
+        <v>3.8570798</v>
       </c>
       <c r="N20">
-        <v>41.71259106666668</v>
+        <v>41.50958686666667</v>
       </c>
       <c r="O20">
-        <v>14.18228096266667</v>
+        <v>14.11325953466667</v>
       </c>
       <c r="P20">
-        <v>27.53031010400001</v>
+        <v>27.39632733200001</v>
       </c>
       <c r="Q20">
-        <v>31.83031010400001</v>
+        <v>31.69632733200001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1266688522951508</v>
+        <v>0.1273707391603741</v>
       </c>
       <c r="T20">
-        <v>1.053992242177593</v>
+        <v>1.063140180967817</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.41536071849928</v>
+        <v>11.76192068068353</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.109666018719903</v>
+        <v>0.1093097385577823</v>
       </c>
       <c r="C21">
-        <v>280.5016988753915</v>
+        <v>278.3877396317066</v>
       </c>
       <c r="D21">
-        <v>321.7626988753915</v>
+        <v>323.5677396317066</v>
       </c>
       <c r="E21">
-        <v>-234.039</v>
+        <v>-230.12</v>
       </c>
       <c r="F21">
-        <v>74.461</v>
+        <v>78.38</v>
       </c>
       <c r="G21">
         <v>33.2</v>
@@ -3003,28 +3003,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M21">
-        <v>3.8570798</v>
+        <v>4.060084</v>
       </c>
       <c r="N21">
-        <v>41.50958686666667</v>
+        <v>41.30658266666667</v>
       </c>
       <c r="O21">
-        <v>14.11325953466667</v>
+        <v>14.04423810666667</v>
       </c>
       <c r="P21">
-        <v>27.39632733200001</v>
+        <v>27.26234456</v>
       </c>
       <c r="Q21">
-        <v>31.69632733200001</v>
+        <v>31.56234456</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1273707391603741</v>
+        <v>0.1280901731972279</v>
       </c>
       <c r="T21">
-        <v>1.063140180967817</v>
+        <v>1.072516818227796</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.76192068068353</v>
+        <v>11.17382464664935</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1093097385577823</v>
+        <v>0.1089534583956617</v>
       </c>
       <c r="C22">
-        <v>278.3877396317066</v>
+        <v>276.2941466586782</v>
       </c>
       <c r="D22">
-        <v>323.5677396317066</v>
+        <v>325.3931466586782</v>
       </c>
       <c r="E22">
-        <v>-230.12</v>
+        <v>-226.201</v>
       </c>
       <c r="F22">
-        <v>78.38</v>
+        <v>82.29900000000001</v>
       </c>
       <c r="G22">
         <v>33.2</v>
@@ -3085,28 +3085,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M22">
-        <v>4.060084</v>
+        <v>4.2630882</v>
       </c>
       <c r="N22">
-        <v>41.30658266666667</v>
+        <v>41.10357846666668</v>
       </c>
       <c r="O22">
-        <v>14.04423810666667</v>
+        <v>13.97521667866667</v>
       </c>
       <c r="P22">
-        <v>27.26234456</v>
+        <v>27.12836178800001</v>
       </c>
       <c r="Q22">
-        <v>31.56234456</v>
+        <v>31.42836178800001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1280901731972279</v>
+        <v>0.1288278207540021</v>
       </c>
       <c r="T22">
-        <v>1.072516818227796</v>
+        <v>1.082130838709547</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.17382464664935</v>
+        <v>10.64173775871367</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1089534583956617</v>
+        <v>0.108597178233541</v>
       </c>
       <c r="C23">
-        <v>276.2941466586782</v>
+        <v>274.2212666007775</v>
       </c>
       <c r="D23">
-        <v>325.3931466586782</v>
+        <v>327.2392666007775</v>
       </c>
       <c r="E23">
-        <v>-226.201</v>
+        <v>-222.282</v>
       </c>
       <c r="F23">
-        <v>82.29899999999999</v>
+        <v>86.21799999999999</v>
       </c>
       <c r="G23">
         <v>33.2</v>
@@ -3167,28 +3167,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M23">
-        <v>4.263088199999999</v>
+        <v>4.466092399999999</v>
       </c>
       <c r="N23">
-        <v>41.10357846666668</v>
+        <v>40.90057426666667</v>
       </c>
       <c r="O23">
-        <v>13.97521667866667</v>
+        <v>13.90619525066667</v>
       </c>
       <c r="P23">
-        <v>27.12836178800001</v>
+        <v>26.994379016</v>
       </c>
       <c r="Q23">
-        <v>31.42836178800001</v>
+        <v>31.294379016</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1288278207540021</v>
+        <v>0.1295843823506936</v>
       </c>
       <c r="T23">
-        <v>1.082130838709547</v>
+        <v>1.091991372536983</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.64173775871367</v>
+        <v>10.15802240604486</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.108597178233541</v>
+        <v>0.1084989580714203</v>
       </c>
       <c r="C24">
-        <v>274.2212666007775</v>
+        <v>270.8148986253985</v>
       </c>
       <c r="D24">
-        <v>327.2392666007775</v>
+        <v>327.7518986253986</v>
       </c>
       <c r="E24">
-        <v>-222.282</v>
+        <v>-218.363</v>
       </c>
       <c r="F24">
-        <v>86.21799999999999</v>
+        <v>90.137</v>
       </c>
       <c r="G24">
         <v>33.2</v>
@@ -3249,45 +3249,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M24">
-        <v>4.466092399999999</v>
+        <v>4.822329499999999</v>
       </c>
       <c r="N24">
-        <v>40.90057426666667</v>
+        <v>40.54433716666667</v>
       </c>
       <c r="O24">
-        <v>13.90619525066667</v>
+        <v>13.78507463666667</v>
       </c>
       <c r="P24">
-        <v>26.994379016</v>
+        <v>26.75926253</v>
       </c>
       <c r="Q24">
-        <v>31.294379016</v>
+        <v>31.05926253</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1295843823506936</v>
+        <v>0.1303605948979485</v>
       </c>
       <c r="T24">
-        <v>1.091991372536983</v>
+        <v>1.102108024126172</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.15802240604486</v>
+        <v>9.407624814245207</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1084989580714203</v>
+        <v>0.1081538979092997</v>
       </c>
       <c r="C25">
-        <v>270.8148986253985</v>
+        <v>268.7096444707592</v>
       </c>
       <c r="D25">
-        <v>327.7518986253986</v>
+        <v>329.5656444707592</v>
       </c>
       <c r="E25">
-        <v>-218.363</v>
+        <v>-214.444</v>
       </c>
       <c r="F25">
-        <v>90.137</v>
+        <v>94.056</v>
       </c>
       <c r="G25">
         <v>33.2</v>
@@ -3331,28 +3331,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M25">
-        <v>4.822329499999999</v>
+        <v>5.031995999999999</v>
       </c>
       <c r="N25">
-        <v>40.54433716666667</v>
+        <v>40.33467066666667</v>
       </c>
       <c r="O25">
-        <v>13.78507463666667</v>
+        <v>13.71378802666667</v>
       </c>
       <c r="P25">
-        <v>26.75926253</v>
+        <v>26.62088264</v>
       </c>
       <c r="Q25">
-        <v>31.05926253</v>
+        <v>30.92088264000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1303605948979485</v>
+        <v>0.1311572340911838</v>
       </c>
       <c r="T25">
-        <v>1.102108024126172</v>
+        <v>1.11249090338876</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.407624814245207</v>
+        <v>9.015640446984989</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1081538979092997</v>
+        <v>0.107808837747179</v>
       </c>
       <c r="C26">
-        <v>268.7096444707592</v>
+        <v>266.6245761947197</v>
       </c>
       <c r="D26">
-        <v>329.5656444707592</v>
+        <v>331.3995761947197</v>
       </c>
       <c r="E26">
-        <v>-214.444</v>
+        <v>-210.525</v>
       </c>
       <c r="F26">
-        <v>94.056</v>
+        <v>97.97499999999999</v>
       </c>
       <c r="G26">
         <v>33.2</v>
@@ -3413,28 +3413,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M26">
-        <v>5.031995999999999</v>
+        <v>5.241662499999999</v>
       </c>
       <c r="N26">
-        <v>40.33467066666667</v>
+        <v>40.12500416666668</v>
       </c>
       <c r="O26">
-        <v>13.71378802666667</v>
+        <v>13.64250141666667</v>
       </c>
       <c r="P26">
-        <v>26.62088264</v>
+        <v>26.48250275000001</v>
       </c>
       <c r="Q26">
-        <v>30.92088264000001</v>
+        <v>30.78250275000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1311572340911838</v>
+        <v>0.1319751169962387</v>
       </c>
       <c r="T26">
-        <v>1.11249090338876</v>
+        <v>1.123150659431683</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.015640446984989</v>
+        <v>8.655014829105591</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.107808837747179</v>
+        <v>0.1074637775850583</v>
       </c>
       <c r="C27">
-        <v>266.6245761947197</v>
+        <v>264.5600326676586</v>
       </c>
       <c r="D27">
-        <v>331.3995761947197</v>
+        <v>333.2540326676586</v>
       </c>
       <c r="E27">
-        <v>-210.525</v>
+        <v>-206.606</v>
       </c>
       <c r="F27">
-        <v>97.97499999999999</v>
+        <v>101.894</v>
       </c>
       <c r="G27">
         <v>33.2</v>
@@ -3495,28 +3495,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M27">
-        <v>5.241662499999999</v>
+        <v>5.451328999999999</v>
       </c>
       <c r="N27">
-        <v>40.12500416666668</v>
+        <v>39.91533766666667</v>
       </c>
       <c r="O27">
-        <v>13.64250141666667</v>
+        <v>13.57121480666667</v>
       </c>
       <c r="P27">
-        <v>26.48250275000001</v>
+        <v>26.34412286</v>
       </c>
       <c r="Q27">
-        <v>30.78250275000001</v>
+        <v>30.64412286</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1319751169962387</v>
+        <v>0.1328151048446734</v>
       </c>
       <c r="T27">
-        <v>1.123150659431683</v>
+        <v>1.134098516989281</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.655014829105591</v>
+        <v>8.322129643370758</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1074637775850583</v>
+        <v>0.1071187174229377</v>
       </c>
       <c r="C28">
-        <v>264.5600326676586</v>
+        <v>262.5163603876845</v>
       </c>
       <c r="D28">
-        <v>333.2540326676586</v>
+        <v>335.1293603876845</v>
       </c>
       <c r="E28">
-        <v>-206.606</v>
+        <v>-202.687</v>
       </c>
       <c r="F28">
-        <v>101.894</v>
+        <v>105.813</v>
       </c>
       <c r="G28">
         <v>33.2</v>
@@ -3577,28 +3577,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M28">
-        <v>5.451328999999999</v>
+        <v>5.6609955</v>
       </c>
       <c r="N28">
-        <v>39.91533766666667</v>
+        <v>39.70567116666668</v>
       </c>
       <c r="O28">
-        <v>13.57121480666667</v>
+        <v>13.49992819666667</v>
       </c>
       <c r="P28">
-        <v>26.34412286</v>
+        <v>26.20574297</v>
       </c>
       <c r="Q28">
-        <v>30.64412286</v>
+        <v>30.50574297</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1328151048446734</v>
+        <v>0.1336781060588187</v>
       </c>
       <c r="T28">
-        <v>1.134098516989281</v>
+        <v>1.145346315849826</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.322129643370758</v>
+        <v>8.013902619542211</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1071187174229377</v>
+        <v>0.106773657260817</v>
       </c>
       <c r="C29">
-        <v>262.5163603876845</v>
+        <v>260.4939136964703</v>
       </c>
       <c r="D29">
-        <v>335.1293603876845</v>
+        <v>337.0259136964702</v>
       </c>
       <c r="E29">
-        <v>-202.687</v>
+        <v>-198.768</v>
       </c>
       <c r="F29">
-        <v>105.813</v>
+        <v>109.732</v>
       </c>
       <c r="G29">
         <v>33.2</v>
@@ -3659,28 +3659,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M29">
-        <v>5.6609955</v>
+        <v>5.870662</v>
       </c>
       <c r="N29">
-        <v>39.70567116666668</v>
+        <v>39.49600466666667</v>
       </c>
       <c r="O29">
-        <v>13.49992819666667</v>
+        <v>13.42864158666667</v>
       </c>
       <c r="P29">
-        <v>26.20574297</v>
+        <v>26.06736308</v>
       </c>
       <c r="Q29">
-        <v>30.50574297</v>
+        <v>30.36736308</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1336781060588187</v>
+        <v>0.1345650795289125</v>
       </c>
       <c r="T29">
-        <v>1.145346315849826</v>
+        <v>1.156906553567608</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.013902619542211</v>
+        <v>7.727691811701418</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.106773657260817</v>
+        <v>0.1065817170986963</v>
       </c>
       <c r="C30">
-        <v>260.4939136964703</v>
+        <v>257.6391943979964</v>
       </c>
       <c r="D30">
-        <v>337.0259136964702</v>
+        <v>338.0901943979964</v>
       </c>
       <c r="E30">
-        <v>-198.768</v>
+        <v>-194.849</v>
       </c>
       <c r="F30">
-        <v>109.732</v>
+        <v>113.651</v>
       </c>
       <c r="G30">
         <v>33.2</v>
@@ -3741,45 +3741,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M30">
-        <v>5.870662</v>
+        <v>6.1712493</v>
       </c>
       <c r="N30">
-        <v>39.49600466666667</v>
+        <v>39.19541736666667</v>
       </c>
       <c r="O30">
-        <v>13.42864158666667</v>
+        <v>13.32644190466667</v>
       </c>
       <c r="P30">
-        <v>26.06736308</v>
+        <v>25.86897546200001</v>
       </c>
       <c r="Q30">
-        <v>30.36736308</v>
+        <v>30.16897546200001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1345650795289125</v>
+        <v>0.1354770381671779</v>
       </c>
       <c r="T30">
-        <v>1.156906553567608</v>
+        <v>1.168792431784483</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.34</v>
       </c>
       <c r="W30">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.727691811701418</v>
+        <v>7.351293791788103</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1065817170986963</v>
+        <v>0.1062419369365757</v>
       </c>
       <c r="C31">
-        <v>257.6391943979964</v>
+        <v>255.6208009451444</v>
       </c>
       <c r="D31">
-        <v>338.0901943979964</v>
+        <v>339.9908009451444</v>
       </c>
       <c r="E31">
-        <v>-194.849</v>
+        <v>-190.93</v>
       </c>
       <c r="F31">
-        <v>113.651</v>
+        <v>117.57</v>
       </c>
       <c r="G31">
         <v>33.2</v>
@@ -3823,28 +3823,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M31">
-        <v>6.171249299999999</v>
+        <v>6.384050999999999</v>
       </c>
       <c r="N31">
-        <v>39.19541736666667</v>
+        <v>38.98261566666667</v>
       </c>
       <c r="O31">
-        <v>13.32644190466667</v>
+        <v>13.25408932666667</v>
       </c>
       <c r="P31">
-        <v>25.86897546200001</v>
+        <v>25.72852634</v>
       </c>
       <c r="Q31">
-        <v>30.16897546200001</v>
+        <v>30.02852634</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1354770381671779</v>
+        <v>0.1364150527665367</v>
       </c>
       <c r="T31">
-        <v>1.168792431784483</v>
+        <v>1.18101790652184</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.351293791788104</v>
+        <v>7.106250665395167</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1062419369365757</v>
+        <v>0.105902156774455</v>
       </c>
       <c r="C32">
-        <v>255.6208009451444</v>
+        <v>253.6238971836903</v>
       </c>
       <c r="D32">
-        <v>339.9908009451444</v>
+        <v>341.9128971836903</v>
       </c>
       <c r="E32">
-        <v>-190.93</v>
+        <v>-187.011</v>
       </c>
       <c r="F32">
-        <v>117.57</v>
+        <v>121.489</v>
       </c>
       <c r="G32">
         <v>33.2</v>
@@ -3905,28 +3905,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M32">
-        <v>6.384050999999999</v>
+        <v>6.596852699999999</v>
       </c>
       <c r="N32">
-        <v>38.98261566666667</v>
+        <v>38.76981396666667</v>
       </c>
       <c r="O32">
-        <v>13.25408932666667</v>
+        <v>13.18173674866667</v>
       </c>
       <c r="P32">
-        <v>25.72852634</v>
+        <v>25.588077218</v>
       </c>
       <c r="Q32">
-        <v>30.02852634</v>
+        <v>29.888077218</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1364150527665367</v>
+        <v>0.1373802561948623</v>
       </c>
       <c r="T32">
-        <v>1.18101790652184</v>
+        <v>1.193597742845788</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.106250665395167</v>
+        <v>6.877016772963064</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.105902156774455</v>
+        <v>0.1055623766123343</v>
       </c>
       <c r="C33">
-        <v>253.6238971836903</v>
+        <v>251.6488496538175</v>
       </c>
       <c r="D33">
-        <v>341.9128971836903</v>
+        <v>343.8568496538175</v>
       </c>
       <c r="E33">
-        <v>-187.011</v>
+        <v>-183.092</v>
       </c>
       <c r="F33">
-        <v>121.489</v>
+        <v>125.408</v>
       </c>
       <c r="G33">
         <v>33.2</v>
@@ -3987,28 +3987,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M33">
-        <v>6.596852699999999</v>
+        <v>6.8096544</v>
       </c>
       <c r="N33">
-        <v>38.76981396666667</v>
+        <v>38.55701226666667</v>
       </c>
       <c r="O33">
-        <v>13.18173674866667</v>
+        <v>13.10938417066667</v>
       </c>
       <c r="P33">
-        <v>25.588077218</v>
+        <v>25.447628096</v>
       </c>
       <c r="Q33">
-        <v>29.888077218</v>
+        <v>29.747628096</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1373802561948623</v>
+        <v>0.1383738479593152</v>
       </c>
       <c r="T33">
-        <v>1.193597742845788</v>
+        <v>1.206547574355733</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.877016772963064</v>
+        <v>6.662109998807968</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1055623766123343</v>
+        <v>0.1052225964502137</v>
       </c>
       <c r="C34">
-        <v>251.6488496538175</v>
+        <v>249.6960332792598</v>
       </c>
       <c r="D34">
-        <v>343.8568496538175</v>
+        <v>345.8230332792598</v>
       </c>
       <c r="E34">
-        <v>-183.092</v>
+        <v>-179.173</v>
       </c>
       <c r="F34">
-        <v>125.408</v>
+        <v>129.327</v>
       </c>
       <c r="G34">
         <v>33.2</v>
@@ -4069,28 +4069,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M34">
-        <v>6.8096544</v>
+        <v>7.0224561</v>
       </c>
       <c r="N34">
-        <v>38.55701226666667</v>
+        <v>38.34421056666667</v>
       </c>
       <c r="O34">
-        <v>13.10938417066667</v>
+        <v>13.03703159266667</v>
       </c>
       <c r="P34">
-        <v>25.447628096</v>
+        <v>25.307178974</v>
       </c>
       <c r="Q34">
-        <v>29.747628096</v>
+        <v>29.607178974</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1383738479593152</v>
+        <v>0.1393970991794234</v>
       </c>
       <c r="T34">
-        <v>1.206547574355733</v>
+        <v>1.219883968000304</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.662109998807968</v>
+        <v>6.460227877631969</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1052225964502137</v>
+        <v>0.104882816288093</v>
       </c>
       <c r="C35">
-        <v>249.6960332792598</v>
+        <v>247.7658316083667</v>
       </c>
       <c r="D35">
-        <v>345.8230332792598</v>
+        <v>347.8118316083667</v>
       </c>
       <c r="E35">
-        <v>-179.173</v>
+        <v>-175.254</v>
       </c>
       <c r="F35">
-        <v>129.327</v>
+        <v>133.246</v>
       </c>
       <c r="G35">
         <v>33.2</v>
@@ -4151,28 +4151,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M35">
-        <v>7.0224561</v>
+        <v>7.2352578</v>
       </c>
       <c r="N35">
-        <v>38.34421056666667</v>
+        <v>38.13140886666667</v>
       </c>
       <c r="O35">
-        <v>13.03703159266667</v>
+        <v>12.96467901466667</v>
       </c>
       <c r="P35">
-        <v>25.307178974</v>
+        <v>25.166729852</v>
       </c>
       <c r="Q35">
-        <v>29.607178974</v>
+        <v>29.466729852</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1393970991794234</v>
+        <v>0.1404513580122621</v>
       </c>
       <c r="T35">
-        <v>1.219883968000304</v>
+        <v>1.233624494785619</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.460227877631969</v>
+        <v>6.270221175348675</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.104882816288093</v>
+        <v>0.1047740361259723</v>
       </c>
       <c r="C36">
-        <v>247.7658316083667</v>
+        <v>244.4883855855952</v>
       </c>
       <c r="D36">
-        <v>347.8118316083667</v>
+        <v>348.4533855855952</v>
       </c>
       <c r="E36">
-        <v>-175.254</v>
+        <v>-171.335</v>
       </c>
       <c r="F36">
-        <v>133.246</v>
+        <v>137.165</v>
       </c>
       <c r="G36">
         <v>33.2</v>
@@ -4233,45 +4233,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M36">
-        <v>7.2352578</v>
+        <v>7.5852245</v>
       </c>
       <c r="N36">
-        <v>38.13140886666667</v>
+        <v>37.78144216666667</v>
       </c>
       <c r="O36">
-        <v>12.96467901466667</v>
+        <v>12.84569033666667</v>
       </c>
       <c r="P36">
-        <v>25.166729852</v>
+        <v>24.93575183</v>
       </c>
       <c r="Q36">
-        <v>29.466729852</v>
+        <v>29.23575183</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1404513580122621</v>
+        <v>0.141538055578419</v>
       </c>
       <c r="T36">
-        <v>1.233624494785619</v>
+        <v>1.247787807010483</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.34</v>
       </c>
       <c r="W36">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.270221175348675</v>
+        <v>5.980926031479579</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1047740361259723</v>
+        <v>0.1044408559638517</v>
       </c>
       <c r="C37">
-        <v>244.4883855855952</v>
+        <v>242.5491956274622</v>
       </c>
       <c r="D37">
-        <v>348.4533855855952</v>
+        <v>350.4331956274622</v>
       </c>
       <c r="E37">
-        <v>-171.335</v>
+        <v>-167.416</v>
       </c>
       <c r="F37">
-        <v>137.165</v>
+        <v>141.084</v>
       </c>
       <c r="G37">
         <v>33.2</v>
@@ -4315,28 +4315,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M37">
-        <v>7.5852245</v>
+        <v>7.8019452</v>
       </c>
       <c r="N37">
-        <v>37.78144216666667</v>
+        <v>37.56472146666668</v>
       </c>
       <c r="O37">
-        <v>12.84569033666667</v>
+        <v>12.77200529866667</v>
       </c>
       <c r="P37">
-        <v>24.93575183</v>
+        <v>24.79271616800001</v>
       </c>
       <c r="Q37">
-        <v>29.23575183</v>
+        <v>29.09271616800001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.141538055578419</v>
+        <v>0.1426587124435183</v>
       </c>
       <c r="T37">
-        <v>1.247787807010483</v>
+        <v>1.262393722742374</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.980926031479579</v>
+        <v>5.814789197271812</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1044408559638517</v>
+        <v>0.104107675801731</v>
       </c>
       <c r="C38">
-        <v>242.5491956274622</v>
+        <v>240.632631624545</v>
       </c>
       <c r="D38">
-        <v>350.4331956274622</v>
+        <v>352.435631624545</v>
       </c>
       <c r="E38">
-        <v>-167.416</v>
+        <v>-163.497</v>
       </c>
       <c r="F38">
-        <v>141.084</v>
+        <v>145.003</v>
       </c>
       <c r="G38">
         <v>33.2</v>
@@ -4397,28 +4397,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M38">
-        <v>7.801945199999999</v>
+        <v>8.0186659</v>
       </c>
       <c r="N38">
-        <v>37.56472146666668</v>
+        <v>37.34800076666667</v>
       </c>
       <c r="O38">
-        <v>12.77200529866667</v>
+        <v>12.69832026066667</v>
       </c>
       <c r="P38">
-        <v>24.79271616800001</v>
+        <v>24.649680506</v>
       </c>
       <c r="Q38">
-        <v>29.09271616800001</v>
+        <v>28.949680506</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1426587124435182</v>
+        <v>0.1438149457170333</v>
       </c>
       <c r="T38">
-        <v>1.262393722742373</v>
+        <v>1.277463318338768</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.814789197271814</v>
+        <v>5.657632732480683</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.104107675801731</v>
+        <v>0.1037744956396104</v>
       </c>
       <c r="C39">
-        <v>240.632631624545</v>
+        <v>238.7390836717989</v>
       </c>
       <c r="D39">
-        <v>352.435631624545</v>
+        <v>354.4610836717989</v>
       </c>
       <c r="E39">
-        <v>-163.497</v>
+        <v>-159.578</v>
       </c>
       <c r="F39">
-        <v>145.003</v>
+        <v>148.922</v>
       </c>
       <c r="G39">
         <v>33.2</v>
@@ -4479,28 +4479,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M39">
-        <v>8.0186659</v>
+        <v>8.2353866</v>
       </c>
       <c r="N39">
-        <v>37.34800076666667</v>
+        <v>37.13128006666668</v>
       </c>
       <c r="O39">
-        <v>12.69832026066667</v>
+        <v>12.62463522266667</v>
       </c>
       <c r="P39">
-        <v>24.649680506</v>
+        <v>24.50664484400001</v>
       </c>
       <c r="Q39">
-        <v>28.949680506</v>
+        <v>28.80664484400001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1438149457170333</v>
+        <v>0.1450084768380812</v>
       </c>
       <c r="T39">
-        <v>1.277463318338768</v>
+        <v>1.293019029922144</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.657632732480683</v>
+        <v>5.508747660573297</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1037744956396104</v>
+        <v>0.1034413154774897</v>
       </c>
       <c r="C40">
-        <v>238.7390836717989</v>
+        <v>236.8689508835364</v>
       </c>
       <c r="D40">
-        <v>354.4610836717989</v>
+        <v>356.5099508835364</v>
       </c>
       <c r="E40">
-        <v>-159.578</v>
+        <v>-155.659</v>
       </c>
       <c r="F40">
-        <v>148.922</v>
+        <v>152.841</v>
       </c>
       <c r="G40">
         <v>33.2</v>
@@ -4561,28 +4561,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M40">
-        <v>8.2353866</v>
+        <v>8.452107300000002</v>
       </c>
       <c r="N40">
-        <v>37.13128006666668</v>
+        <v>36.91455936666667</v>
       </c>
       <c r="O40">
-        <v>12.62463522266667</v>
+        <v>12.55095018466667</v>
       </c>
       <c r="P40">
-        <v>24.50664484400001</v>
+        <v>24.363609182</v>
       </c>
       <c r="Q40">
-        <v>28.80664484400001</v>
+        <v>28.66360918200001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1450084768380812</v>
+        <v>0.1462411401270323</v>
       </c>
       <c r="T40">
-        <v>1.293019029922144</v>
+        <v>1.309084764836122</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.508747660573297</v>
+        <v>5.367497720558595</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1034413154774897</v>
+        <v>0.103108135315369</v>
       </c>
       <c r="C41">
-        <v>236.8689508835364</v>
+        <v>235.0226416556115</v>
       </c>
       <c r="D41">
-        <v>356.5099508835364</v>
+        <v>358.5826416556115</v>
       </c>
       <c r="E41">
-        <v>-155.659</v>
+        <v>-151.74</v>
       </c>
       <c r="F41">
-        <v>152.841</v>
+        <v>156.76</v>
       </c>
       <c r="G41">
         <v>33.2</v>
@@ -4643,28 +4643,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M41">
-        <v>8.452107300000002</v>
+        <v>8.668828</v>
       </c>
       <c r="N41">
-        <v>36.91455936666667</v>
+        <v>36.69783866666668</v>
       </c>
       <c r="O41">
-        <v>12.55095018466667</v>
+        <v>12.47726514666667</v>
       </c>
       <c r="P41">
-        <v>24.363609182</v>
+        <v>24.22057352000001</v>
       </c>
       <c r="Q41">
-        <v>28.66360918200001</v>
+        <v>28.52057352000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1462411401270323</v>
+        <v>0.1475148921922817</v>
       </c>
       <c r="T41">
-        <v>1.309084764836122</v>
+        <v>1.325686024247233</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.367497720558595</v>
+        <v>5.233310277544632</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.103108135315369</v>
+        <v>0.1027749551532483</v>
       </c>
       <c r="C42">
-        <v>235.0226416556115</v>
+        <v>233.2005739368064</v>
       </c>
       <c r="D42">
-        <v>358.5826416556115</v>
+        <v>360.6795739368064</v>
       </c>
       <c r="E42">
-        <v>-151.74</v>
+        <v>-147.821</v>
       </c>
       <c r="F42">
-        <v>156.76</v>
+        <v>160.679</v>
       </c>
       <c r="G42">
         <v>33.2</v>
@@ -4725,28 +4725,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M42">
-        <v>8.668828</v>
+        <v>8.885548700000001</v>
       </c>
       <c r="N42">
-        <v>36.69783866666668</v>
+        <v>36.48111796666667</v>
       </c>
       <c r="O42">
-        <v>12.47726514666667</v>
+        <v>12.40358010866667</v>
       </c>
       <c r="P42">
-        <v>24.22057352000001</v>
+        <v>24.077537858</v>
       </c>
       <c r="Q42">
-        <v>28.52057352000001</v>
+        <v>28.377537858</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1475148921922817</v>
+        <v>0.1488318222936413</v>
       </c>
       <c r="T42">
-        <v>1.325686024247233</v>
+        <v>1.342850038214652</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.233310277544632</v>
+        <v>5.105668563458177</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1027749551532483</v>
+        <v>0.1024417749911277</v>
       </c>
       <c r="C43">
-        <v>233.2005739368064</v>
+        <v>231.403175509792</v>
       </c>
       <c r="D43">
-        <v>360.6795739368064</v>
+        <v>362.801175509792</v>
       </c>
       <c r="E43">
-        <v>-147.821</v>
+        <v>-143.902</v>
       </c>
       <c r="F43">
-        <v>160.679</v>
+        <v>164.598</v>
       </c>
       <c r="G43">
         <v>33.2</v>
@@ -4807,28 +4807,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M43">
-        <v>8.885548700000001</v>
+        <v>9.102269400000001</v>
       </c>
       <c r="N43">
-        <v>36.48111796666667</v>
+        <v>36.26439726666668</v>
       </c>
       <c r="O43">
-        <v>12.40358010866667</v>
+        <v>12.32989507066667</v>
       </c>
       <c r="P43">
-        <v>24.077537858</v>
+        <v>23.934502196</v>
       </c>
       <c r="Q43">
-        <v>28.377537858</v>
+        <v>28.234502196</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1488318222936413</v>
+        <v>0.1501941637778064</v>
       </c>
       <c r="T43">
-        <v>1.342850038214652</v>
+        <v>1.360605914732673</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.105668563458177</v>
+        <v>4.984105026232982</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1024417749911277</v>
+        <v>0.102108594829007</v>
       </c>
       <c r="C44">
-        <v>231.403175509792</v>
+        <v>229.6308842820672</v>
       </c>
       <c r="D44">
-        <v>362.801175509792</v>
+        <v>364.9478842820672</v>
       </c>
       <c r="E44">
-        <v>-143.902</v>
+        <v>-139.983</v>
       </c>
       <c r="F44">
-        <v>164.598</v>
+        <v>168.517</v>
       </c>
       <c r="G44">
         <v>33.2</v>
@@ -4889,28 +4889,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M44">
-        <v>9.102269399999999</v>
+        <v>9.318990100000001</v>
       </c>
       <c r="N44">
-        <v>36.26439726666668</v>
+        <v>36.04767656666667</v>
       </c>
       <c r="O44">
-        <v>12.32989507066667</v>
+        <v>12.25621003266667</v>
       </c>
       <c r="P44">
-        <v>23.934502196</v>
+        <v>23.791466534</v>
       </c>
       <c r="Q44">
-        <v>28.234502196</v>
+        <v>28.091466534</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1501941637778064</v>
+        <v>0.1516043067175562</v>
       </c>
       <c r="T44">
-        <v>1.360605914732672</v>
+        <v>1.378984804461851</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.984105026232983</v>
+        <v>4.868195607018261</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.102108594829007</v>
+        <v>0.1017754146668864</v>
       </c>
       <c r="C45">
-        <v>229.6308842820672</v>
+        <v>227.8841485872859</v>
       </c>
       <c r="D45">
-        <v>364.9478842820672</v>
+        <v>367.1201485872859</v>
       </c>
       <c r="E45">
-        <v>-139.983</v>
+        <v>-136.064</v>
       </c>
       <c r="F45">
-        <v>168.517</v>
+        <v>172.436</v>
       </c>
       <c r="G45">
         <v>33.2</v>
@@ -4971,28 +4971,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M45">
-        <v>9.318990100000001</v>
+        <v>9.535710799999999</v>
       </c>
       <c r="N45">
-        <v>36.04767656666667</v>
+        <v>35.83095586666668</v>
       </c>
       <c r="O45">
-        <v>12.25621003266667</v>
+        <v>12.18252499466667</v>
       </c>
       <c r="P45">
-        <v>23.791466534</v>
+        <v>23.64843087200001</v>
       </c>
       <c r="Q45">
-        <v>28.091466534</v>
+        <v>27.94843087200001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1516043067175562</v>
+        <v>0.1530648119051542</v>
       </c>
       <c r="T45">
-        <v>1.378984804461851</v>
+        <v>1.398020083109929</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.868195607018261</v>
+        <v>4.757554797767848</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1017754146668864</v>
+        <v>0.1014422345047657</v>
       </c>
       <c r="C46">
-        <v>227.8841485872859</v>
+        <v>226.1634274974113</v>
       </c>
       <c r="D46">
-        <v>367.1201485872859</v>
+        <v>369.3184274974113</v>
       </c>
       <c r="E46">
-        <v>-136.064</v>
+        <v>-132.145</v>
       </c>
       <c r="F46">
-        <v>172.436</v>
+        <v>176.355</v>
       </c>
       <c r="G46">
         <v>33.2</v>
@@ -5053,28 +5053,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M46">
-        <v>9.535710799999999</v>
+        <v>9.7524315</v>
       </c>
       <c r="N46">
-        <v>35.83095586666668</v>
+        <v>35.61423516666667</v>
       </c>
       <c r="O46">
-        <v>12.18252499466667</v>
+        <v>12.10883995666667</v>
       </c>
       <c r="P46">
-        <v>23.64843087200001</v>
+        <v>23.50539521</v>
       </c>
       <c r="Q46">
-        <v>27.94843087200001</v>
+        <v>27.80539521</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1530648119051542</v>
+        <v>0.1545784263723013</v>
       </c>
       <c r="T46">
-        <v>1.398020083109929</v>
+        <v>1.417747553708846</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.757554797767848</v>
+        <v>4.65183135781745</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1014422345047657</v>
+        <v>0.101109054342645</v>
       </c>
       <c r="C47">
-        <v>226.1634274974113</v>
+        <v>224.4691911461519</v>
       </c>
       <c r="D47">
-        <v>369.3184274974113</v>
+        <v>371.5431911461519</v>
       </c>
       <c r="E47">
-        <v>-132.145</v>
+        <v>-128.226</v>
       </c>
       <c r="F47">
-        <v>176.355</v>
+        <v>180.274</v>
       </c>
       <c r="G47">
         <v>33.2</v>
@@ -5135,28 +5135,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M47">
-        <v>9.7524315</v>
+        <v>9.9691522</v>
       </c>
       <c r="N47">
-        <v>35.61423516666667</v>
+        <v>35.39751446666668</v>
       </c>
       <c r="O47">
-        <v>12.10883995666667</v>
+        <v>12.03515491866667</v>
       </c>
       <c r="P47">
-        <v>23.50539521</v>
+        <v>23.36235954800001</v>
       </c>
       <c r="Q47">
-        <v>27.80539521</v>
+        <v>27.66235954800001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1545784263723013</v>
+        <v>0.1561481006345278</v>
       </c>
       <c r="T47">
-        <v>1.417747553708846</v>
+        <v>1.438205671366982</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.65183135781745</v>
+        <v>4.550704589169245</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.101109054342645</v>
+        <v>0.1015513741805244</v>
       </c>
       <c r="C48">
-        <v>224.4691911461519</v>
+        <v>217.6024445392109</v>
       </c>
       <c r="D48">
-        <v>371.5431911461519</v>
+        <v>368.5954445392109</v>
       </c>
       <c r="E48">
-        <v>-128.226</v>
+        <v>-124.307</v>
       </c>
       <c r="F48">
-        <v>180.274</v>
+        <v>184.193</v>
       </c>
       <c r="G48">
         <v>33.2</v>
@@ -5217,45 +5217,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M48">
-        <v>9.9691522</v>
+        <v>10.6463554</v>
       </c>
       <c r="N48">
-        <v>35.39751446666668</v>
+        <v>34.72031126666667</v>
       </c>
       <c r="O48">
-        <v>12.03515491866667</v>
+        <v>11.80490583066667</v>
       </c>
       <c r="P48">
-        <v>23.36235954800001</v>
+        <v>22.915405436</v>
       </c>
       <c r="Q48">
-        <v>27.66235954800001</v>
+        <v>27.215405436</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1561481006345278</v>
+        <v>0.1577770078877818</v>
       </c>
       <c r="T48">
-        <v>1.438205671366982</v>
+        <v>1.459435793465049</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.34</v>
       </c>
       <c r="W48">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.550704589169245</v>
+        <v>4.261239171732578</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1015513741805244</v>
+        <v>0.1012346940184037</v>
       </c>
       <c r="C49">
-        <v>217.6024445392109</v>
+        <v>215.7891090007999</v>
       </c>
       <c r="D49">
-        <v>368.5954445392109</v>
+        <v>370.7011090007999</v>
       </c>
       <c r="E49">
-        <v>-124.307</v>
+        <v>-120.388</v>
       </c>
       <c r="F49">
-        <v>184.193</v>
+        <v>188.112</v>
       </c>
       <c r="G49">
         <v>33.2</v>
@@ -5299,28 +5299,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M49">
-        <v>10.6463554</v>
+        <v>10.8728736</v>
       </c>
       <c r="N49">
-        <v>34.72031126666667</v>
+        <v>34.49379306666668</v>
       </c>
       <c r="O49">
-        <v>11.80490583066667</v>
+        <v>11.72788964266667</v>
       </c>
       <c r="P49">
-        <v>22.915405436</v>
+        <v>22.765903424</v>
       </c>
       <c r="Q49">
-        <v>27.215405436</v>
+        <v>27.06590342400001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1577770078877818</v>
+        <v>0.1594685654200071</v>
       </c>
       <c r="T49">
-        <v>1.459435793465049</v>
+        <v>1.481482458720732</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.261239171732578</v>
+        <v>4.172463355654818</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1012346940184037</v>
+        <v>0.100918013856283</v>
       </c>
       <c r="C50">
-        <v>215.7891090007999</v>
+        <v>213.9999696231871</v>
       </c>
       <c r="D50">
-        <v>370.7011090007999</v>
+        <v>372.8309696231871</v>
       </c>
       <c r="E50">
-        <v>-120.388</v>
+        <v>-116.469</v>
       </c>
       <c r="F50">
-        <v>188.112</v>
+        <v>192.031</v>
       </c>
       <c r="G50">
         <v>33.2</v>
@@ -5381,28 +5381,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M50">
-        <v>10.8728736</v>
+        <v>11.0993918</v>
       </c>
       <c r="N50">
-        <v>34.49379306666668</v>
+        <v>34.26727486666667</v>
       </c>
       <c r="O50">
-        <v>11.72788964266667</v>
+        <v>11.65087345466667</v>
       </c>
       <c r="P50">
-        <v>22.765903424</v>
+        <v>22.61640141200001</v>
       </c>
       <c r="Q50">
-        <v>27.06590342400001</v>
+        <v>26.91640141200001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1594685654200071</v>
+        <v>0.1612264585417314</v>
       </c>
       <c r="T50">
-        <v>1.481482458720732</v>
+        <v>1.504393699084482</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.172463355654818</v>
+        <v>4.087311042274107</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.100918013856283</v>
+        <v>0.1006013336941624</v>
       </c>
       <c r="C51">
-        <v>213.9999696231871</v>
+        <v>212.2354458730316</v>
       </c>
       <c r="D51">
-        <v>372.8309696231871</v>
+        <v>374.9854458730316</v>
       </c>
       <c r="E51">
-        <v>-116.469</v>
+        <v>-112.55</v>
       </c>
       <c r="F51">
-        <v>192.031</v>
+        <v>195.95</v>
       </c>
       <c r="G51">
         <v>33.2</v>
@@ -5463,28 +5463,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M51">
-        <v>11.0993918</v>
+        <v>11.32591</v>
       </c>
       <c r="N51">
-        <v>34.26727486666667</v>
+        <v>34.04075666666667</v>
       </c>
       <c r="O51">
-        <v>11.65087345466667</v>
+        <v>11.57385726666667</v>
       </c>
       <c r="P51">
-        <v>22.61640141200001</v>
+        <v>22.4668994</v>
       </c>
       <c r="Q51">
-        <v>26.91640141200001</v>
+        <v>26.7668994</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1612264585417314</v>
+        <v>0.1630546673883247</v>
       </c>
       <c r="T51">
-        <v>1.504393699084482</v>
+        <v>1.528221389062782</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.087311042274107</v>
+        <v>4.005564821428624</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1006013336941624</v>
+        <v>0.1014627535320417</v>
       </c>
       <c r="C52">
-        <v>212.2354458730316</v>
+        <v>202.5132852046483</v>
       </c>
       <c r="D52">
-        <v>374.9854458730316</v>
+        <v>369.1822852046483</v>
       </c>
       <c r="E52">
-        <v>-112.55</v>
+        <v>-108.631</v>
       </c>
       <c r="F52">
-        <v>195.95</v>
+        <v>199.869</v>
       </c>
       <c r="G52">
         <v>33.2</v>
@@ -5545,45 +5545,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M52">
-        <v>11.32591</v>
+        <v>12.2519697</v>
       </c>
       <c r="N52">
-        <v>34.04075666666667</v>
+        <v>33.11469696666667</v>
       </c>
       <c r="O52">
-        <v>11.57385726666667</v>
+        <v>11.25899696866667</v>
       </c>
       <c r="P52">
-        <v>22.4668994</v>
+        <v>21.855699998</v>
       </c>
       <c r="Q52">
-        <v>26.7668994</v>
+        <v>26.155699998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1630546673883247</v>
+        <v>0.1649574970041668</v>
       </c>
       <c r="T52">
-        <v>1.528221389062782</v>
+        <v>1.553021637815707</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.34</v>
       </c>
       <c r="W52">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.005564821428624</v>
+        <v>3.702805979569691</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1014627535320417</v>
+        <v>0.101169173369921</v>
       </c>
       <c r="C53">
-        <v>202.5132852046483</v>
+        <v>200.5517750594876</v>
       </c>
       <c r="D53">
-        <v>369.1822852046483</v>
+        <v>371.1397750594876</v>
       </c>
       <c r="E53">
-        <v>-108.631</v>
+        <v>-104.712</v>
       </c>
       <c r="F53">
-        <v>199.869</v>
+        <v>203.788</v>
       </c>
       <c r="G53">
         <v>33.2</v>
@@ -5627,28 +5627,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M53">
-        <v>12.2519697</v>
+        <v>12.4922044</v>
       </c>
       <c r="N53">
-        <v>33.11469696666667</v>
+        <v>32.87446226666668</v>
       </c>
       <c r="O53">
-        <v>11.25899696866667</v>
+        <v>11.17731717066667</v>
       </c>
       <c r="P53">
-        <v>21.855699998</v>
+        <v>21.69714509600001</v>
       </c>
       <c r="Q53">
-        <v>26.155699998</v>
+        <v>25.99714509600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1649574970041668</v>
+        <v>0.1669396111873355</v>
       </c>
       <c r="T53">
-        <v>1.553021637815707</v>
+        <v>1.578855230266669</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.702805979569691</v>
+        <v>3.631598172270274</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.101169173369921</v>
+        <v>0.1008755932078004</v>
       </c>
       <c r="C54">
-        <v>200.5517750594876</v>
+        <v>198.6111336932348</v>
       </c>
       <c r="D54">
-        <v>371.1397750594876</v>
+        <v>373.1181336932348</v>
       </c>
       <c r="E54">
-        <v>-104.712</v>
+        <v>-100.793</v>
       </c>
       <c r="F54">
-        <v>203.788</v>
+        <v>207.707</v>
       </c>
       <c r="G54">
         <v>33.2</v>
@@ -5709,28 +5709,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M54">
-        <v>12.4922044</v>
+        <v>12.7324391</v>
       </c>
       <c r="N54">
-        <v>32.87446226666668</v>
+        <v>32.63422756666667</v>
       </c>
       <c r="O54">
-        <v>11.17731717066667</v>
+        <v>11.09563737266667</v>
       </c>
       <c r="P54">
-        <v>21.69714509600001</v>
+        <v>21.538590194</v>
       </c>
       <c r="Q54">
-        <v>25.99714509600001</v>
+        <v>25.83859019400001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1669396111873355</v>
+        <v>0.1690060706548944</v>
       </c>
       <c r="T54">
-        <v>1.578855230266669</v>
+        <v>1.605788124524056</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.631598172270274</v>
+        <v>3.563077452038759</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1008755932078004</v>
+        <v>0.1015799330456797</v>
       </c>
       <c r="C55">
-        <v>198.6111336932348</v>
+        <v>189.9807267150276</v>
       </c>
       <c r="D55">
-        <v>373.1181336932348</v>
+        <v>368.4067267150276</v>
       </c>
       <c r="E55">
-        <v>-100.793</v>
+        <v>-96.874</v>
       </c>
       <c r="F55">
-        <v>207.707</v>
+        <v>211.626</v>
       </c>
       <c r="G55">
         <v>33.2</v>
@@ -5791,45 +5791,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M55">
-        <v>12.7324391</v>
+        <v>13.5652266</v>
       </c>
       <c r="N55">
-        <v>32.63422756666667</v>
+        <v>31.80144006666667</v>
       </c>
       <c r="O55">
-        <v>11.09563737266667</v>
+        <v>10.81248962266667</v>
       </c>
       <c r="P55">
-        <v>21.538590194</v>
+        <v>20.988950444</v>
       </c>
       <c r="Q55">
-        <v>25.83859019400001</v>
+        <v>25.288950444</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1690060706548944</v>
+        <v>0.1711623761862603</v>
       </c>
       <c r="T55">
-        <v>1.605788124524056</v>
+        <v>1.633892014183939</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.34</v>
       </c>
       <c r="W55">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.563077452038759</v>
+        <v>3.344335336548427</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1015799330456797</v>
+        <v>0.101304832883559</v>
       </c>
       <c r="C56">
-        <v>189.9807267150276</v>
+        <v>187.8876713216579</v>
       </c>
       <c r="D56">
-        <v>368.4067267150276</v>
+        <v>370.232671321658</v>
       </c>
       <c r="E56">
-        <v>-96.874</v>
+        <v>-92.95499999999998</v>
       </c>
       <c r="F56">
-        <v>211.626</v>
+        <v>215.545</v>
       </c>
       <c r="G56">
         <v>33.2</v>
@@ -5873,28 +5873,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M56">
-        <v>13.5652266</v>
+        <v>13.8164345</v>
       </c>
       <c r="N56">
-        <v>31.80144006666667</v>
+        <v>31.55023216666667</v>
       </c>
       <c r="O56">
-        <v>10.81248962266667</v>
+        <v>10.72707893666667</v>
       </c>
       <c r="P56">
-        <v>20.988950444</v>
+        <v>20.82315323</v>
       </c>
       <c r="Q56">
-        <v>25.288950444</v>
+        <v>25.12315323</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1711623761862603</v>
+        <v>0.1734145175190201</v>
       </c>
       <c r="T56">
-        <v>1.633892014183939</v>
+        <v>1.663244965606482</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.344335336548427</v>
+        <v>3.283529239520274</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.101304832883559</v>
+        <v>0.1010297327214384</v>
       </c>
       <c r="C57">
-        <v>187.8876713216579</v>
+        <v>185.8128060455514</v>
       </c>
       <c r="D57">
-        <v>370.232671321658</v>
+        <v>372.0768060455515</v>
       </c>
       <c r="E57">
-        <v>-92.95499999999998</v>
+        <v>-89.036</v>
       </c>
       <c r="F57">
-        <v>215.545</v>
+        <v>219.464</v>
       </c>
       <c r="G57">
         <v>33.2</v>
@@ -5955,28 +5955,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M57">
-        <v>13.8164345</v>
+        <v>14.0676424</v>
       </c>
       <c r="N57">
-        <v>31.55023216666667</v>
+        <v>31.29902426666667</v>
       </c>
       <c r="O57">
-        <v>10.72707893666667</v>
+        <v>10.64166825066667</v>
       </c>
       <c r="P57">
-        <v>20.82315323</v>
+        <v>20.657356016</v>
       </c>
       <c r="Q57">
-        <v>25.12315323</v>
+        <v>24.957356016</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1734145175190201</v>
+        <v>0.17576902891236</v>
       </c>
       <c r="T57">
-        <v>1.663244965606482</v>
+        <v>1.693932142093686</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.283529239520274</v>
+        <v>3.224894788814554</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1010297327214384</v>
+        <v>0.1007546325593177</v>
       </c>
       <c r="C58">
-        <v>185.8128060455514</v>
+        <v>183.7564040631796</v>
       </c>
       <c r="D58">
-        <v>372.0768060455515</v>
+        <v>373.9394040631796</v>
       </c>
       <c r="E58">
-        <v>-89.036</v>
+        <v>-85.11699999999999</v>
       </c>
       <c r="F58">
-        <v>219.464</v>
+        <v>223.383</v>
       </c>
       <c r="G58">
         <v>33.2</v>
@@ -6037,28 +6037,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M58">
-        <v>14.0676424</v>
+        <v>14.3188503</v>
       </c>
       <c r="N58">
-        <v>31.29902426666667</v>
+        <v>31.04781636666667</v>
       </c>
       <c r="O58">
-        <v>10.64166825066667</v>
+        <v>10.55625756466667</v>
       </c>
       <c r="P58">
-        <v>20.657356016</v>
+        <v>20.491558802</v>
       </c>
       <c r="Q58">
-        <v>24.957356016</v>
+        <v>24.791558802</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.17576902891236</v>
+        <v>0.1782330524635296</v>
       </c>
       <c r="T58">
-        <v>1.693932142093686</v>
+        <v>1.726046629115179</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.224894788814554</v>
+        <v>3.168317687256404</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1007546325593177</v>
+        <v>0.100479532397197</v>
       </c>
       <c r="C59">
-        <v>183.7564040631796</v>
+        <v>181.7187440485661</v>
       </c>
       <c r="D59">
-        <v>373.9394040631796</v>
+        <v>375.8207440485661</v>
       </c>
       <c r="E59">
-        <v>-85.11699999999999</v>
+        <v>-81.19799999999998</v>
       </c>
       <c r="F59">
-        <v>223.383</v>
+        <v>227.302</v>
       </c>
       <c r="G59">
         <v>33.2</v>
@@ -6119,28 +6119,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M59">
-        <v>14.3188503</v>
+        <v>14.5700582</v>
       </c>
       <c r="N59">
-        <v>31.04781636666667</v>
+        <v>30.79660846666667</v>
       </c>
       <c r="O59">
-        <v>10.55625756466667</v>
+        <v>10.47084687866667</v>
       </c>
       <c r="P59">
-        <v>20.491558802</v>
+        <v>20.325761588</v>
       </c>
       <c r="Q59">
-        <v>24.791558802</v>
+        <v>24.625761588</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1782330524635296</v>
+        <v>0.1808144104695168</v>
       </c>
       <c r="T59">
-        <v>1.726046629115179</v>
+        <v>1.75969037742341</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.168317687256404</v>
+        <v>3.113691520234742</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.100479532397197</v>
+        <v>0.1002044322350764</v>
       </c>
       <c r="C60">
-        <v>181.7187440485661</v>
+        <v>179.7001103122804</v>
       </c>
       <c r="D60">
-        <v>375.820744048566</v>
+        <v>377.7211103122804</v>
       </c>
       <c r="E60">
-        <v>-81.19800000000004</v>
+        <v>-77.27900000000002</v>
       </c>
       <c r="F60">
-        <v>227.302</v>
+        <v>231.221</v>
       </c>
       <c r="G60">
         <v>33.2</v>
@@ -6201,28 +6201,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M60">
-        <v>14.5700582</v>
+        <v>14.8212661</v>
       </c>
       <c r="N60">
-        <v>30.79660846666668</v>
+        <v>30.54540056666668</v>
       </c>
       <c r="O60">
-        <v>10.47084687866667</v>
+        <v>10.38543619266667</v>
       </c>
       <c r="P60">
-        <v>20.32576158800001</v>
+        <v>20.159964374</v>
       </c>
       <c r="Q60">
-        <v>24.62576158800001</v>
+        <v>24.45996437400001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1808144104695168</v>
+        <v>0.1835216883782351</v>
       </c>
       <c r="T60">
-        <v>1.75969037742341</v>
+        <v>1.794975284185701</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.113691520234743</v>
+        <v>3.060917087688391</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1002044322350764</v>
+        <v>0.09992933207295571</v>
       </c>
       <c r="C61">
-        <v>179.7001103122804</v>
+        <v>177.7007929446701</v>
       </c>
       <c r="D61">
-        <v>377.7211103122804</v>
+        <v>379.6407929446701</v>
       </c>
       <c r="E61">
-        <v>-77.27900000000002</v>
+        <v>-73.36000000000001</v>
       </c>
       <c r="F61">
-        <v>231.221</v>
+        <v>235.14</v>
       </c>
       <c r="G61">
         <v>33.2</v>
@@ -6283,28 +6283,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M61">
-        <v>14.8212661</v>
+        <v>15.072474</v>
       </c>
       <c r="N61">
-        <v>30.54540056666668</v>
+        <v>30.29419266666667</v>
       </c>
       <c r="O61">
-        <v>10.38543619266667</v>
+        <v>10.30002550666667</v>
       </c>
       <c r="P61">
-        <v>20.159964374</v>
+        <v>19.99416716</v>
       </c>
       <c r="Q61">
-        <v>24.45996437400001</v>
+        <v>24.29416716</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1835216883782351</v>
+        <v>0.1863643301823893</v>
       </c>
       <c r="T61">
-        <v>1.794975284185701</v>
+        <v>1.832024436286106</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.060917087688391</v>
+        <v>3.009901802893584</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09992933207295571</v>
+        <v>0.1027945119108351</v>
       </c>
       <c r="C62">
-        <v>177.7007929446701</v>
+        <v>154.6968124945645</v>
       </c>
       <c r="D62">
-        <v>379.6407929446701</v>
+        <v>360.5558124945645</v>
       </c>
       <c r="E62">
-        <v>-73.36000000000001</v>
+        <v>-69.44100000000003</v>
       </c>
       <c r="F62">
-        <v>235.14</v>
+        <v>239.059</v>
       </c>
       <c r="G62">
         <v>33.2</v>
@@ -6365,45 +6365,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M62">
-        <v>15.072474</v>
+        <v>17.1883421</v>
       </c>
       <c r="N62">
-        <v>30.29419266666667</v>
+        <v>28.17832456666667</v>
       </c>
       <c r="O62">
-        <v>10.30002550666667</v>
+        <v>9.58063035266667</v>
       </c>
       <c r="P62">
-        <v>19.99416716</v>
+        <v>18.597694214</v>
       </c>
       <c r="Q62">
-        <v>24.29416716</v>
+        <v>22.897694214</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1863643301823893</v>
+        <v>0.1893527484893207</v>
       </c>
       <c r="T62">
-        <v>1.832024436286106</v>
+        <v>1.870973544904481</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.34</v>
       </c>
       <c r="W62">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.009901802893584</v>
+        <v>2.639385835046108</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1027945119108351</v>
+        <v>0.1025708917487144</v>
       </c>
       <c r="C63">
-        <v>154.6968124945645</v>
+        <v>152.1980394235419</v>
       </c>
       <c r="D63">
-        <v>360.5558124945645</v>
+        <v>361.9760394235419</v>
       </c>
       <c r="E63">
-        <v>-69.44100000000003</v>
+        <v>-65.52200000000002</v>
       </c>
       <c r="F63">
-        <v>239.059</v>
+        <v>242.978</v>
       </c>
       <c r="G63">
         <v>33.2</v>
@@ -6447,28 +6447,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M63">
-        <v>17.1883421</v>
+        <v>17.4701182</v>
       </c>
       <c r="N63">
-        <v>28.17832456666667</v>
+        <v>27.89654846666667</v>
       </c>
       <c r="O63">
-        <v>9.58063035266667</v>
+        <v>9.484826478666669</v>
       </c>
       <c r="P63">
-        <v>18.597694214</v>
+        <v>18.411721988</v>
       </c>
       <c r="Q63">
-        <v>22.897694214</v>
+        <v>22.711721988</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1893527484893207</v>
+        <v>0.192498451970301</v>
       </c>
       <c r="T63">
-        <v>1.870973544904481</v>
+        <v>1.911972606608034</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.639385835046108</v>
+        <v>2.596815095771171</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1025708917487144</v>
+        <v>0.1023472715865937</v>
       </c>
       <c r="C64">
-        <v>152.1980394235419</v>
+        <v>149.7104991270527</v>
       </c>
       <c r="D64">
-        <v>361.9760394235419</v>
+        <v>363.4074991270527</v>
       </c>
       <c r="E64">
-        <v>-65.52200000000002</v>
+        <v>-61.60300000000001</v>
       </c>
       <c r="F64">
-        <v>242.978</v>
+        <v>246.897</v>
       </c>
       <c r="G64">
         <v>33.2</v>
@@ -6529,28 +6529,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M64">
-        <v>17.4701182</v>
+        <v>17.7518943</v>
       </c>
       <c r="N64">
-        <v>27.89654846666667</v>
+        <v>27.61477236666667</v>
       </c>
       <c r="O64">
-        <v>9.484826478666669</v>
+        <v>9.389022604666669</v>
       </c>
       <c r="P64">
-        <v>18.411721988</v>
+        <v>18.22574976200001</v>
       </c>
       <c r="Q64">
-        <v>22.711721988</v>
+        <v>22.52574976200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.192498451970301</v>
+        <v>0.1958141934772803</v>
       </c>
       <c r="T64">
-        <v>1.911972606608034</v>
+        <v>1.955187833809076</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.596815095771171</v>
+        <v>2.555595808536708</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1023472715865937</v>
+        <v>0.102123651424473</v>
       </c>
       <c r="C65">
-        <v>149.7104991270527</v>
+        <v>147.2343253965751</v>
       </c>
       <c r="D65">
-        <v>363.4074991270527</v>
+        <v>364.8503253965752</v>
       </c>
       <c r="E65">
-        <v>-61.60300000000001</v>
+        <v>-57.684</v>
       </c>
       <c r="F65">
-        <v>246.897</v>
+        <v>250.816</v>
       </c>
       <c r="G65">
         <v>33.2</v>
@@ -6611,28 +6611,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M65">
-        <v>17.7518943</v>
+        <v>18.0336704</v>
       </c>
       <c r="N65">
-        <v>27.61477236666667</v>
+        <v>27.33299626666667</v>
       </c>
       <c r="O65">
-        <v>9.389022604666669</v>
+        <v>9.29321873066667</v>
       </c>
       <c r="P65">
-        <v>18.22574976200001</v>
+        <v>18.039777536</v>
       </c>
       <c r="Q65">
-        <v>22.52574976200001</v>
+        <v>22.339777536</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1958141934772803</v>
+        <v>0.1993141428457585</v>
       </c>
       <c r="T65">
-        <v>1.955187833809076</v>
+        <v>2.000803906965731</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.555595808536708</v>
+        <v>2.515664624028322</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.102123651424473</v>
+        <v>0.1035731312623524</v>
       </c>
       <c r="C66">
-        <v>147.2343253965751</v>
+        <v>134.1615340241717</v>
       </c>
       <c r="D66">
-        <v>364.8503253965752</v>
+        <v>355.6965340241717</v>
       </c>
       <c r="E66">
-        <v>-57.684</v>
+        <v>-53.76500000000001</v>
       </c>
       <c r="F66">
-        <v>250.816</v>
+        <v>254.735</v>
       </c>
       <c r="G66">
         <v>33.2</v>
@@ -6693,45 +6693,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M66">
-        <v>18.0336704</v>
+        <v>19.308913</v>
       </c>
       <c r="N66">
-        <v>27.33299626666667</v>
+        <v>26.05775366666667</v>
       </c>
       <c r="O66">
-        <v>9.29321873066667</v>
+        <v>8.859636246666669</v>
       </c>
       <c r="P66">
-        <v>18.039777536</v>
+        <v>17.19811742</v>
       </c>
       <c r="Q66">
-        <v>22.339777536</v>
+        <v>21.49811742</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1993141428457585</v>
+        <v>0.2030140893210069</v>
       </c>
       <c r="T66">
-        <v>2.000803906965731</v>
+        <v>2.049026612874195</v>
       </c>
       <c r="U66">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.34</v>
       </c>
       <c r="W66">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.515664624028322</v>
+        <v>2.349519450766942</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1035731312623524</v>
+        <v>0.1033752511002317</v>
       </c>
       <c r="C67">
-        <v>134.1615340241717</v>
+        <v>131.4650260927853</v>
       </c>
       <c r="D67">
-        <v>355.6965340241717</v>
+        <v>356.9190260927853</v>
       </c>
       <c r="E67">
-        <v>-53.76500000000001</v>
+        <v>-49.846</v>
       </c>
       <c r="F67">
-        <v>254.735</v>
+        <v>258.654</v>
       </c>
       <c r="G67">
         <v>33.2</v>
@@ -6775,28 +6775,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M67">
-        <v>19.308913</v>
+        <v>19.6059732</v>
       </c>
       <c r="N67">
-        <v>26.05775366666667</v>
+        <v>25.76069346666667</v>
       </c>
       <c r="O67">
-        <v>8.859636246666669</v>
+        <v>8.758635778666669</v>
       </c>
       <c r="P67">
-        <v>17.19811742</v>
+        <v>17.002057688</v>
       </c>
       <c r="Q67">
-        <v>21.49811742</v>
+        <v>21.302057688</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2030140893210069</v>
+        <v>0.2069316797065639</v>
       </c>
       <c r="T67">
-        <v>2.049026612874195</v>
+        <v>2.100085948541981</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.349519450766942</v>
+        <v>2.313920671209868</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1033752511002317</v>
+        <v>0.1031773709381111</v>
       </c>
       <c r="C68">
-        <v>131.4650260927853</v>
+        <v>128.776950298486</v>
       </c>
       <c r="D68">
-        <v>356.9190260927853</v>
+        <v>358.149950298486</v>
       </c>
       <c r="E68">
-        <v>-49.846</v>
+        <v>-45.92700000000002</v>
       </c>
       <c r="F68">
-        <v>258.654</v>
+        <v>262.573</v>
       </c>
       <c r="G68">
         <v>33.2</v>
@@ -6857,28 +6857,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M68">
-        <v>19.6059732</v>
+        <v>19.9030334</v>
       </c>
       <c r="N68">
-        <v>25.76069346666667</v>
+        <v>25.46363326666667</v>
       </c>
       <c r="O68">
-        <v>8.758635778666669</v>
+        <v>8.65763531066667</v>
       </c>
       <c r="P68">
-        <v>17.002057688</v>
+        <v>16.805997956</v>
       </c>
       <c r="Q68">
-        <v>21.302057688</v>
+        <v>21.105997956</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2069316797065639</v>
+        <v>0.2110866998124578</v>
       </c>
       <c r="T68">
-        <v>2.100085948541981</v>
+        <v>2.154239789401753</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.313920671209868</v>
+        <v>2.279384541788825</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1031773709381111</v>
+        <v>0.1029794907759904</v>
       </c>
       <c r="C69">
-        <v>128.776950298486</v>
+        <v>126.0973941841655</v>
       </c>
       <c r="D69">
-        <v>358.149950298486</v>
+        <v>359.3893941841655</v>
       </c>
       <c r="E69">
-        <v>-45.92700000000002</v>
+        <v>-42.00799999999998</v>
       </c>
       <c r="F69">
-        <v>262.573</v>
+        <v>266.492</v>
       </c>
       <c r="G69">
         <v>33.2</v>
@@ -6939,28 +6939,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M69">
-        <v>19.9030334</v>
+        <v>20.2000936</v>
       </c>
       <c r="N69">
-        <v>25.46363326666667</v>
+        <v>25.16657306666667</v>
       </c>
       <c r="O69">
-        <v>8.65763531066667</v>
+        <v>8.55663484266667</v>
       </c>
       <c r="P69">
-        <v>16.805997956</v>
+        <v>16.609938224</v>
       </c>
       <c r="Q69">
-        <v>21.105997956</v>
+        <v>20.909938224</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2110866998124578</v>
+        <v>0.21550140867497</v>
       </c>
       <c r="T69">
-        <v>2.154239789401753</v>
+        <v>2.211778245315262</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.279384541788825</v>
+        <v>2.245864180880165</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1029794907759904</v>
+        <v>0.1027816106138697</v>
       </c>
       <c r="C70">
-        <v>126.0973941841655</v>
+        <v>123.426446508757</v>
       </c>
       <c r="D70">
-        <v>359.3893941841655</v>
+        <v>360.637446508757</v>
       </c>
       <c r="E70">
-        <v>-42.00799999999998</v>
+        <v>-38.089</v>
       </c>
       <c r="F70">
-        <v>266.492</v>
+        <v>270.411</v>
       </c>
       <c r="G70">
         <v>33.2</v>
@@ -7021,28 +7021,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M70">
-        <v>20.2000936</v>
+        <v>20.4971538</v>
       </c>
       <c r="N70">
-        <v>25.16657306666667</v>
+        <v>24.86951286666667</v>
       </c>
       <c r="O70">
-        <v>8.55663484266667</v>
+        <v>8.455634374666669</v>
       </c>
       <c r="P70">
-        <v>16.609938224</v>
+        <v>16.413878492</v>
       </c>
       <c r="Q70">
-        <v>20.909938224</v>
+        <v>20.713878492</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.21550140867497</v>
+        <v>0.2202009374640959</v>
       </c>
       <c r="T70">
-        <v>2.211778245315262</v>
+        <v>2.273028859674803</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.245864180880165</v>
+        <v>2.213315424635525</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1027816106138697</v>
+        <v>0.1025837304517491</v>
       </c>
       <c r="C71">
-        <v>123.426446508757</v>
+        <v>120.7641972684236</v>
       </c>
       <c r="D71">
-        <v>360.637446508757</v>
+        <v>361.8941972684236</v>
       </c>
       <c r="E71">
-        <v>-38.089</v>
+        <v>-34.17000000000002</v>
       </c>
       <c r="F71">
-        <v>270.411</v>
+        <v>274.33</v>
       </c>
       <c r="G71">
         <v>33.2</v>
@@ -7103,28 +7103,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M71">
-        <v>20.4971538</v>
+        <v>20.794214</v>
       </c>
       <c r="N71">
-        <v>24.86951286666667</v>
+        <v>24.57245266666667</v>
       </c>
       <c r="O71">
-        <v>8.455634374666669</v>
+        <v>8.35463390666667</v>
       </c>
       <c r="P71">
-        <v>16.413878492</v>
+        <v>16.21781876</v>
       </c>
       <c r="Q71">
-        <v>20.713878492</v>
+        <v>20.51781876</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2202009374640959</v>
+        <v>0.2252137681724969</v>
       </c>
       <c r="T71">
-        <v>2.273028859674803</v>
+        <v>2.33836284832498</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.213315424635525</v>
+        <v>2.181696632855018</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1025837304517491</v>
+        <v>0.1023858502896284</v>
       </c>
       <c r="C72">
-        <v>120.7641972684236</v>
+        <v>118.1107377181908</v>
       </c>
       <c r="D72">
-        <v>361.8941972684236</v>
+        <v>363.1597377181909</v>
       </c>
       <c r="E72">
-        <v>-34.17000000000002</v>
+        <v>-30.25099999999998</v>
       </c>
       <c r="F72">
-        <v>274.33</v>
+        <v>278.249</v>
       </c>
       <c r="G72">
         <v>33.2</v>
@@ -7185,28 +7185,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M72">
-        <v>20.794214</v>
+        <v>21.0912742</v>
       </c>
       <c r="N72">
-        <v>24.57245266666667</v>
+        <v>24.27539246666667</v>
       </c>
       <c r="O72">
-        <v>8.35463390666667</v>
+        <v>8.253633438666668</v>
       </c>
       <c r="P72">
-        <v>16.21781876</v>
+        <v>16.021759028</v>
       </c>
       <c r="Q72">
-        <v>20.51781876</v>
+        <v>20.321759028</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2252137681724969</v>
+        <v>0.2305723113435462</v>
       </c>
       <c r="T72">
-        <v>2.33836284832498</v>
+        <v>2.40820262929586</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.181696632855018</v>
+        <v>2.15096851126551</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1023858502896284</v>
+        <v>0.1021879701275077</v>
       </c>
       <c r="C73">
-        <v>118.1107377181909</v>
+        <v>115.4661603940361</v>
       </c>
       <c r="D73">
-        <v>363.1597377181909</v>
+        <v>364.4341603940361</v>
       </c>
       <c r="E73">
-        <v>-30.25100000000003</v>
+        <v>-26.33200000000005</v>
       </c>
       <c r="F73">
-        <v>278.249</v>
+        <v>282.1679999999999</v>
       </c>
       <c r="G73">
         <v>33.2</v>
@@ -7267,28 +7267,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M73">
-        <v>21.0912742</v>
+        <v>21.3883344</v>
       </c>
       <c r="N73">
-        <v>24.27539246666667</v>
+        <v>23.97833226666668</v>
       </c>
       <c r="O73">
-        <v>8.25363343866667</v>
+        <v>8.152632970666671</v>
       </c>
       <c r="P73">
-        <v>16.02175902800001</v>
+        <v>15.82569929600001</v>
       </c>
       <c r="Q73">
-        <v>20.32175902800001</v>
+        <v>20.12569929600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2305723113435462</v>
+        <v>0.2363136075982419</v>
       </c>
       <c r="T73">
-        <v>2.408202629295859</v>
+        <v>2.483030966050372</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.150968511265511</v>
+        <v>2.121093948609046</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1021879701275077</v>
+        <v>0.1019900899653871</v>
       </c>
       <c r="C74">
-        <v>115.4661603940361</v>
+        <v>112.8305591354422</v>
       </c>
       <c r="D74">
-        <v>364.4341603940361</v>
+        <v>365.7175591354422</v>
       </c>
       <c r="E74">
-        <v>-26.33200000000005</v>
+        <v>-22.41300000000001</v>
       </c>
       <c r="F74">
-        <v>282.1679999999999</v>
+        <v>286.087</v>
       </c>
       <c r="G74">
         <v>33.2</v>
@@ -7349,28 +7349,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M74">
-        <v>21.3883344</v>
+        <v>21.6853946</v>
       </c>
       <c r="N74">
-        <v>23.97833226666668</v>
+        <v>23.68127206666667</v>
       </c>
       <c r="O74">
-        <v>8.152632970666671</v>
+        <v>8.051632502666669</v>
       </c>
       <c r="P74">
-        <v>15.82569929600001</v>
+        <v>15.629639564</v>
       </c>
       <c r="Q74">
-        <v>20.12569929600001</v>
+        <v>19.92963956400001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2363136075982419</v>
+        <v>0.2424801850569892</v>
       </c>
       <c r="T74">
-        <v>2.483030966050372</v>
+        <v>2.563402142564479</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.121093948609046</v>
+        <v>2.09203786712125</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1019900899653871</v>
+        <v>0.1017922098032664</v>
       </c>
       <c r="C75">
-        <v>112.8305591354422</v>
+        <v>110.2040291084325</v>
       </c>
       <c r="D75">
-        <v>365.7175591354422</v>
+        <v>367.0100291084324</v>
       </c>
       <c r="E75">
-        <v>-22.41300000000001</v>
+        <v>-18.49400000000003</v>
       </c>
       <c r="F75">
-        <v>286.087</v>
+        <v>290.006</v>
       </c>
       <c r="G75">
         <v>33.2</v>
@@ -7431,28 +7431,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M75">
-        <v>21.6853946</v>
+        <v>21.9824548</v>
       </c>
       <c r="N75">
-        <v>23.68127206666667</v>
+        <v>23.38421186666667</v>
       </c>
       <c r="O75">
-        <v>8.051632502666669</v>
+        <v>7.95063203466667</v>
       </c>
       <c r="P75">
-        <v>15.629639564</v>
+        <v>15.433579832</v>
       </c>
       <c r="Q75">
-        <v>19.92963956400001</v>
+        <v>19.733579832</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2424801850569892</v>
+        <v>0.2491211146279477</v>
       </c>
       <c r="T75">
-        <v>2.563402142564479</v>
+        <v>2.649955717271979</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.09203786712125</v>
+        <v>2.063767085133125</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1017922098032664</v>
+        <v>0.1015943296411457</v>
       </c>
       <c r="C76">
-        <v>110.2040291084325</v>
+        <v>107.5866668290932</v>
       </c>
       <c r="D76">
-        <v>367.0100291084324</v>
+        <v>368.3116668290932</v>
       </c>
       <c r="E76">
-        <v>-18.49400000000003</v>
+        <v>-14.57500000000005</v>
       </c>
       <c r="F76">
-        <v>290.006</v>
+        <v>293.925</v>
       </c>
       <c r="G76">
         <v>33.2</v>
@@ -7513,28 +7513,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M76">
-        <v>21.9824548</v>
+        <v>22.279515</v>
       </c>
       <c r="N76">
-        <v>23.38421186666667</v>
+        <v>23.08715166666667</v>
       </c>
       <c r="O76">
-        <v>7.95063203466667</v>
+        <v>7.84963156666667</v>
       </c>
       <c r="P76">
-        <v>15.433579832</v>
+        <v>15.2375201</v>
       </c>
       <c r="Q76">
-        <v>19.733579832</v>
+        <v>19.53752010000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2491211146279477</v>
+        <v>0.2562933185645829</v>
       </c>
       <c r="T76">
-        <v>2.649955717271979</v>
+        <v>2.743433577956079</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.063767085133125</v>
+        <v>2.036250190664683</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1015943296411457</v>
+        <v>0.1013964494790251</v>
       </c>
       <c r="C77">
-        <v>107.5866668290932</v>
+        <v>104.9785701875994</v>
       </c>
       <c r="D77">
-        <v>368.3116668290932</v>
+        <v>369.6225701875994</v>
       </c>
       <c r="E77">
-        <v>-14.57500000000005</v>
+        <v>-10.65600000000001</v>
       </c>
       <c r="F77">
-        <v>293.925</v>
+        <v>297.844</v>
       </c>
       <c r="G77">
         <v>33.2</v>
@@ -7595,28 +7595,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M77">
-        <v>22.279515</v>
+        <v>22.5765752</v>
       </c>
       <c r="N77">
-        <v>23.08715166666667</v>
+        <v>22.79009146666667</v>
       </c>
       <c r="O77">
-        <v>7.84963156666667</v>
+        <v>7.74863109866667</v>
       </c>
       <c r="P77">
-        <v>15.2375201</v>
+        <v>15.041460368</v>
       </c>
       <c r="Q77">
-        <v>19.53752010000001</v>
+        <v>19.341460368</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2562933185645829</v>
+        <v>0.2640632061626045</v>
       </c>
       <c r="T77">
-        <v>2.743433577956079</v>
+        <v>2.844701260363854</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.036250190664683</v>
+        <v>2.009457424998043</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1013964494790251</v>
+        <v>0.1084150093169044</v>
       </c>
       <c r="C78">
-        <v>104.9785701875994</v>
+        <v>59.6283198437294</v>
       </c>
       <c r="D78">
-        <v>369.6225701875994</v>
+        <v>328.1913198437294</v>
       </c>
       <c r="E78">
-        <v>-10.65600000000001</v>
+        <v>-6.737000000000023</v>
       </c>
       <c r="F78">
-        <v>297.844</v>
+        <v>301.763</v>
       </c>
       <c r="G78">
         <v>33.2</v>
@@ -7677,45 +7677,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M78">
-        <v>22.5765752</v>
+        <v>27.15867</v>
       </c>
       <c r="N78">
-        <v>22.79009146666667</v>
+        <v>18.20799666666668</v>
       </c>
       <c r="O78">
-        <v>7.74863109866667</v>
+        <v>6.19071886666667</v>
       </c>
       <c r="P78">
-        <v>15.041460368</v>
+        <v>12.01727780000001</v>
       </c>
       <c r="Q78">
-        <v>19.341460368</v>
+        <v>16.31727780000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2640632061626045</v>
+        <v>0.272508736160454</v>
       </c>
       <c r="T78">
-        <v>2.844701260363854</v>
+        <v>2.954774828198391</v>
       </c>
       <c r="U78">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V78">
         <v>0.34</v>
       </c>
       <c r="W78">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.009457424998043</v>
+        <v>1.670430351216266</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1084150093169044</v>
+        <v>0.1083108491547837</v>
       </c>
       <c r="C79">
-        <v>59.6283198437294</v>
+        <v>56.25617629414927</v>
       </c>
       <c r="D79">
-        <v>328.1913198437294</v>
+        <v>328.7381762941493</v>
       </c>
       <c r="E79">
-        <v>-6.737000000000023</v>
+        <v>-2.817999999999984</v>
       </c>
       <c r="F79">
-        <v>301.763</v>
+        <v>305.682</v>
       </c>
       <c r="G79">
         <v>33.2</v>
@@ -7759,28 +7759,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M79">
-        <v>27.15867</v>
+        <v>27.51138</v>
       </c>
       <c r="N79">
-        <v>18.20799666666668</v>
+        <v>17.85528666666668</v>
       </c>
       <c r="O79">
-        <v>6.19071886666667</v>
+        <v>6.07079746666667</v>
       </c>
       <c r="P79">
-        <v>12.01727780000001</v>
+        <v>11.7844892</v>
       </c>
       <c r="Q79">
-        <v>16.31727780000001</v>
+        <v>16.08448920000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.272508736160454</v>
+        <v>0.2817220416126534</v>
       </c>
       <c r="T79">
-        <v>2.954774828198391</v>
+        <v>3.074855084017887</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.670430351216266</v>
+        <v>1.649014577482725</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1083108491547837</v>
+        <v>0.1082066889926631</v>
       </c>
       <c r="C80">
-        <v>56.25617629414927</v>
+        <v>52.88585821095586</v>
       </c>
       <c r="D80">
-        <v>328.7381762941493</v>
+        <v>329.2868582109559</v>
       </c>
       <c r="E80">
-        <v>-2.817999999999984</v>
+        <v>1.100999999999999</v>
       </c>
       <c r="F80">
-        <v>305.682</v>
+        <v>309.601</v>
       </c>
       <c r="G80">
         <v>33.2</v>
@@ -7841,28 +7841,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M80">
-        <v>27.51138</v>
+        <v>27.86409</v>
       </c>
       <c r="N80">
-        <v>17.85528666666668</v>
+        <v>17.50257666666668</v>
       </c>
       <c r="O80">
-        <v>6.07079746666667</v>
+        <v>5.95087606666667</v>
       </c>
       <c r="P80">
-        <v>11.7844892</v>
+        <v>11.55170060000001</v>
       </c>
       <c r="Q80">
-        <v>16.08448920000001</v>
+        <v>15.85170060000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2817220416126534</v>
+        <v>0.2918128047269671</v>
       </c>
       <c r="T80">
-        <v>3.074855084017887</v>
+        <v>3.206371554677335</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.649014577482725</v>
+        <v>1.628140975236108</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1082066889926631</v>
+        <v>0.1081025288305424</v>
       </c>
       <c r="C81">
-        <v>52.88585821095586</v>
+        <v>49.51737474983912</v>
       </c>
       <c r="D81">
-        <v>329.2868582109559</v>
+        <v>329.8373747498391</v>
       </c>
       <c r="E81">
-        <v>1.100999999999999</v>
+        <v>5.019999999999982</v>
       </c>
       <c r="F81">
-        <v>309.601</v>
+        <v>313.52</v>
       </c>
       <c r="G81">
         <v>33.2</v>
@@ -7923,28 +7923,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M81">
-        <v>27.86409</v>
+        <v>28.2168</v>
       </c>
       <c r="N81">
-        <v>17.50257666666668</v>
+        <v>17.14986666666668</v>
       </c>
       <c r="O81">
-        <v>5.95087606666667</v>
+        <v>5.830954666666671</v>
       </c>
       <c r="P81">
-        <v>11.55170060000001</v>
+        <v>11.31891200000001</v>
       </c>
       <c r="Q81">
-        <v>15.85170060000001</v>
+        <v>15.61891200000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2918128047269671</v>
+        <v>0.3029126441527121</v>
       </c>
       <c r="T81">
-        <v>3.206371554677335</v>
+        <v>3.351039672402727</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.628140975236108</v>
+        <v>1.607789213045657</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1081025288305424</v>
+        <v>0.1079983686684217</v>
       </c>
       <c r="C82">
-        <v>49.51737474983912</v>
+        <v>46.15073512781856</v>
       </c>
       <c r="D82">
-        <v>329.8373747498391</v>
+        <v>330.3897351278186</v>
       </c>
       <c r="E82">
-        <v>5.019999999999982</v>
+        <v>8.939000000000021</v>
       </c>
       <c r="F82">
-        <v>313.52</v>
+        <v>317.439</v>
       </c>
       <c r="G82">
         <v>33.2</v>
@@ -8005,28 +8005,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M82">
-        <v>28.2168</v>
+        <v>28.56951</v>
       </c>
       <c r="N82">
-        <v>17.14986666666668</v>
+        <v>16.79715666666667</v>
       </c>
       <c r="O82">
-        <v>5.830954666666671</v>
+        <v>5.71103326666667</v>
       </c>
       <c r="P82">
-        <v>11.31891200000001</v>
+        <v>11.0861234</v>
       </c>
       <c r="Q82">
-        <v>15.61891200000001</v>
+        <v>15.3861234</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3029126441527121</v>
+        <v>0.3151808877285356</v>
       </c>
       <c r="T82">
-        <v>3.351039672402727</v>
+        <v>3.510936013046583</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.607789213045657</v>
+        <v>1.587939963501883</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1079983686684217</v>
+        <v>0.1078942085063011</v>
       </c>
       <c r="C83">
-        <v>46.15073512781856</v>
+        <v>42.78594862375871</v>
       </c>
       <c r="D83">
-        <v>330.3897351278186</v>
+        <v>330.9439486237587</v>
       </c>
       <c r="E83">
-        <v>8.939000000000021</v>
+        <v>12.858</v>
       </c>
       <c r="F83">
-        <v>317.439</v>
+        <v>321.358</v>
       </c>
       <c r="G83">
         <v>33.2</v>
@@ -8087,28 +8087,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M83">
-        <v>28.56951</v>
+        <v>28.92222</v>
       </c>
       <c r="N83">
-        <v>16.79715666666667</v>
+        <v>16.44444666666667</v>
       </c>
       <c r="O83">
-        <v>5.71103326666667</v>
+        <v>5.59111186666667</v>
       </c>
       <c r="P83">
-        <v>11.0861234</v>
+        <v>10.85333480000001</v>
       </c>
       <c r="Q83">
-        <v>15.3861234</v>
+        <v>15.15333480000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3151808877285356</v>
+        <v>0.3288122694794506</v>
       </c>
       <c r="T83">
-        <v>3.510936013046583</v>
+        <v>3.688598613761978</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.587939963501883</v>
+        <v>1.568574841995762</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1078942085063011</v>
+        <v>0.1077900483441804</v>
       </c>
       <c r="C84">
-        <v>42.78594862375871</v>
+        <v>39.42302457888815</v>
       </c>
       <c r="D84">
-        <v>330.9439486237587</v>
+        <v>331.5000245788881</v>
       </c>
       <c r="E84">
-        <v>12.858</v>
+        <v>16.77699999999999</v>
       </c>
       <c r="F84">
-        <v>321.358</v>
+        <v>325.277</v>
       </c>
       <c r="G84">
         <v>33.2</v>
@@ -8169,28 +8169,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M84">
-        <v>28.92222</v>
+        <v>29.27493</v>
       </c>
       <c r="N84">
-        <v>16.44444666666667</v>
+        <v>16.09173666666668</v>
       </c>
       <c r="O84">
-        <v>5.59111186666667</v>
+        <v>5.471190466666671</v>
       </c>
       <c r="P84">
-        <v>10.85333480000001</v>
+        <v>10.62054620000001</v>
       </c>
       <c r="Q84">
-        <v>15.15333480000001</v>
+        <v>14.92054620000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3288122694794506</v>
+        <v>0.3440473432010614</v>
       </c>
       <c r="T84">
-        <v>3.688598613761978</v>
+        <v>3.887162696914477</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.568574841995762</v>
+        <v>1.549676349923524</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1077900483441804</v>
+        <v>0.1076858881820597</v>
       </c>
       <c r="C85">
-        <v>39.42302457888815</v>
+        <v>36.06197239732393</v>
       </c>
       <c r="D85">
-        <v>331.5000245788881</v>
+        <v>332.057972397324</v>
       </c>
       <c r="E85">
-        <v>16.77699999999999</v>
+        <v>20.69600000000003</v>
       </c>
       <c r="F85">
-        <v>325.277</v>
+        <v>329.196</v>
       </c>
       <c r="G85">
         <v>33.2</v>
@@ -8251,28 +8251,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M85">
-        <v>29.27493</v>
+        <v>29.62764</v>
       </c>
       <c r="N85">
-        <v>16.09173666666668</v>
+        <v>15.73902666666667</v>
       </c>
       <c r="O85">
-        <v>5.471190466666671</v>
+        <v>5.35126906666667</v>
       </c>
       <c r="P85">
-        <v>10.62054620000001</v>
+        <v>10.3877576</v>
       </c>
       <c r="Q85">
-        <v>14.92054620000001</v>
+        <v>14.6877576</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3440473432010614</v>
+        <v>0.3611868011378736</v>
       </c>
       <c r="T85">
-        <v>3.887162696914477</v>
+        <v>4.11054729046104</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.549676349923524</v>
+        <v>1.531227821948244</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1076858881820597</v>
+        <v>0.1075817280199391</v>
       </c>
       <c r="C86">
-        <v>36.06197239732387</v>
+        <v>32.70280154660259</v>
       </c>
       <c r="D86">
-        <v>332.0579723973239</v>
+        <v>332.6178015466025</v>
       </c>
       <c r="E86">
-        <v>20.69599999999997</v>
+        <v>24.61499999999995</v>
       </c>
       <c r="F86">
-        <v>329.196</v>
+        <v>333.115</v>
       </c>
       <c r="G86">
         <v>33.2</v>
@@ -8333,28 +8333,28 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M86">
-        <v>29.62764</v>
+        <v>29.98034999999999</v>
       </c>
       <c r="N86">
-        <v>15.73902666666668</v>
+        <v>15.38631666666668</v>
       </c>
       <c r="O86">
-        <v>5.351269066666671</v>
+        <v>5.231347666666672</v>
       </c>
       <c r="P86">
-        <v>10.38775760000001</v>
+        <v>10.15496900000001</v>
       </c>
       <c r="Q86">
-        <v>14.68775760000001</v>
+        <v>14.45496900000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3611868011378734</v>
+        <v>0.3806115201329272</v>
       </c>
       <c r="T86">
-        <v>4.110547290461037</v>
+        <v>4.363716496480474</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.531227821948244</v>
+        <v>1.513213376984147</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1075817280199391</v>
+        <v>0.1449985568918237</v>
       </c>
       <c r="C87">
-        <v>32.70280154660259</v>
+        <v>-96.67672681353855</v>
       </c>
       <c r="D87">
-        <v>332.6178015466025</v>
+        <v>207.1572731864614</v>
       </c>
       <c r="E87">
-        <v>24.61499999999995</v>
+        <v>28.53399999999999</v>
       </c>
       <c r="F87">
-        <v>333.115</v>
+        <v>337.034</v>
       </c>
       <c r="G87">
         <v>33.2</v>
@@ -8415,45 +8415,45 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M87">
-        <v>29.98034999999999</v>
+        <v>49.4765912</v>
       </c>
       <c r="N87">
-        <v>15.38631666666668</v>
+        <v>-4.109924533333327</v>
       </c>
       <c r="O87">
-        <v>5.231347666666672</v>
+        <v>-1.397374341333331</v>
       </c>
       <c r="P87">
-        <v>10.15496900000001</v>
+        <v>-2.712550191999996</v>
       </c>
       <c r="Q87">
-        <v>14.45496900000001</v>
+        <v>1.587449808000005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3806115201329272</v>
+        <v>0.4150659773370099</v>
       </c>
       <c r="T87">
-        <v>4.363716496480474</v>
+        <v>4.812773575576928</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.34</v>
+        <v>0.3117568590025796</v>
       </c>
       <c r="W87">
-        <v>0.05939999999999999</v>
+        <v>0.1010340930984213</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.513213376984147</v>
+        <v>0.9169319382428811</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1449985568918237</v>
+        <v>0.1460085568918237</v>
       </c>
       <c r="C88">
-        <v>-96.67672681353855</v>
+        <v>-102.683660742616</v>
       </c>
       <c r="D88">
-        <v>207.1572731864614</v>
+        <v>205.069339257384</v>
       </c>
       <c r="E88">
-        <v>28.53399999999999</v>
+        <v>32.45299999999997</v>
       </c>
       <c r="F88">
-        <v>337.034</v>
+        <v>340.953</v>
       </c>
       <c r="G88">
         <v>33.2</v>
@@ -8497,37 +8497,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M88">
-        <v>49.4765912</v>
+        <v>50.0519004</v>
       </c>
       <c r="N88">
-        <v>-4.109924533333327</v>
+        <v>-4.685233733333327</v>
       </c>
       <c r="O88">
-        <v>-1.397374341333331</v>
+        <v>-1.592979469333331</v>
       </c>
       <c r="P88">
-        <v>-2.712550191999996</v>
+        <v>-3.092254263999996</v>
       </c>
       <c r="Q88">
-        <v>1.587449808000005</v>
+        <v>1.207745736000005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4150659773370099</v>
+        <v>0.4434710525167799</v>
       </c>
       <c r="T88">
-        <v>4.812773575576928</v>
+        <v>5.182986927544384</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.3117568590025796</v>
+        <v>0.3081734468301361</v>
       </c>
       <c r="W88">
-        <v>0.1010340930984213</v>
+        <v>0.101560138005336</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9169319382428811</v>
+        <v>0.906392490676871</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1460085568918237</v>
+        <v>0.1470185568918237</v>
       </c>
       <c r="C89">
-        <v>-102.683660742616</v>
+        <v>-108.6489261608368</v>
       </c>
       <c r="D89">
-        <v>205.069339257384</v>
+        <v>203.0230738391631</v>
       </c>
       <c r="E89">
-        <v>32.45299999999997</v>
+        <v>36.37199999999996</v>
       </c>
       <c r="F89">
-        <v>340.953</v>
+        <v>344.872</v>
       </c>
       <c r="G89">
         <v>33.2</v>
@@ -8579,37 +8579,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M89">
-        <v>50.0519004</v>
+        <v>50.6272096</v>
       </c>
       <c r="N89">
-        <v>-4.685233733333327</v>
+        <v>-5.260542933333326</v>
       </c>
       <c r="O89">
-        <v>-1.592979469333331</v>
+        <v>-1.788584597333331</v>
       </c>
       <c r="P89">
-        <v>-3.092254263999996</v>
+        <v>-3.471958335999995</v>
       </c>
       <c r="Q89">
-        <v>1.207745736000005</v>
+        <v>0.8280416640000055</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4434710525167799</v>
+        <v>0.4766103068931783</v>
       </c>
       <c r="T89">
-        <v>5.182986927544384</v>
+        <v>5.614902504839751</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.3081734468301361</v>
+        <v>0.30467147584343</v>
       </c>
       <c r="W89">
-        <v>0.101560138005336</v>
+        <v>0.1020742273461845</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.906392490676871</v>
+        <v>0.8960925760100883</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1470185568918237</v>
+        <v>0.1480285568918237</v>
       </c>
       <c r="C90">
-        <v>-108.6489261608368</v>
+        <v>-114.5737581006787</v>
       </c>
       <c r="D90">
-        <v>203.0230738391631</v>
+        <v>201.0172418993213</v>
       </c>
       <c r="E90">
-        <v>36.37199999999996</v>
+        <v>40.291</v>
       </c>
       <c r="F90">
-        <v>344.872</v>
+        <v>348.791</v>
       </c>
       <c r="G90">
         <v>33.2</v>
@@ -8661,37 +8661,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M90">
-        <v>50.6272096</v>
+        <v>51.20251880000001</v>
       </c>
       <c r="N90">
-        <v>-5.260542933333326</v>
+        <v>-5.835852133333333</v>
       </c>
       <c r="O90">
-        <v>-1.788584597333331</v>
+        <v>-1.984189725333333</v>
       </c>
       <c r="P90">
-        <v>-3.471958335999995</v>
+        <v>-3.851662407999999</v>
       </c>
       <c r="Q90">
-        <v>0.8280416640000055</v>
+        <v>0.4483375920000015</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4766103068931783</v>
+        <v>0.5157748802471036</v>
       </c>
       <c r="T90">
-        <v>5.614902504839751</v>
+        <v>6.12534818709791</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.30467147584343</v>
+        <v>0.3012482008339533</v>
       </c>
       <c r="W90">
-        <v>0.1020742273461845</v>
+        <v>0.1025767641175757</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8960925760100883</v>
+        <v>0.8860241200998625</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1480285568918237</v>
+        <v>0.1490385568918237</v>
       </c>
       <c r="C91">
-        <v>-114.5737581006787</v>
+        <v>-120.459343264505</v>
       </c>
       <c r="D91">
-        <v>201.0172418993213</v>
+        <v>199.0506567354949</v>
       </c>
       <c r="E91">
-        <v>40.291</v>
+        <v>44.20999999999998</v>
       </c>
       <c r="F91">
-        <v>348.791</v>
+        <v>352.71</v>
       </c>
       <c r="G91">
         <v>33.2</v>
@@ -8743,37 +8743,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M91">
-        <v>51.20251880000001</v>
+        <v>51.777828</v>
       </c>
       <c r="N91">
-        <v>-5.835852133333333</v>
+        <v>-6.411161333333325</v>
       </c>
       <c r="O91">
-        <v>-1.984189725333333</v>
+        <v>-2.179794853333331</v>
       </c>
       <c r="P91">
-        <v>-3.851662407999999</v>
+        <v>-4.231366479999995</v>
       </c>
       <c r="Q91">
-        <v>0.4483375920000015</v>
+        <v>0.06863352000000589</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5157748802471036</v>
+        <v>0.5627723682718139</v>
       </c>
       <c r="T91">
-        <v>6.12534818709791</v>
+        <v>6.7378830058077</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.3012482008339533</v>
+        <v>0.2979009986024649</v>
       </c>
       <c r="W91">
-        <v>0.1025767641175757</v>
+        <v>0.1030681334051581</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8860241200998625</v>
+        <v>0.8761794076543086</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1490385568918237</v>
+        <v>0.1500485568918237</v>
       </c>
       <c r="C92">
-        <v>-120.459343264505</v>
+        <v>-126.3068223657695</v>
       </c>
       <c r="D92">
-        <v>199.0506567354949</v>
+        <v>197.1221776342305</v>
       </c>
       <c r="E92">
-        <v>44.20999999999998</v>
+        <v>48.12900000000002</v>
       </c>
       <c r="F92">
-        <v>352.71</v>
+        <v>356.629</v>
       </c>
       <c r="G92">
         <v>33.2</v>
@@ -8825,37 +8825,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M92">
-        <v>51.777828</v>
+        <v>52.35313720000001</v>
       </c>
       <c r="N92">
-        <v>-6.411161333333325</v>
+        <v>-6.986470533333332</v>
       </c>
       <c r="O92">
-        <v>-2.179794853333331</v>
+        <v>-2.375399981333333</v>
       </c>
       <c r="P92">
-        <v>-4.231366479999995</v>
+        <v>-4.611070551999999</v>
       </c>
       <c r="Q92">
-        <v>0.06863352000000589</v>
+        <v>-0.3110705519999986</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5627723682718139</v>
+        <v>0.6202137425242378</v>
       </c>
       <c r="T92">
-        <v>6.7378830058077</v>
+        <v>7.486536673119669</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2979009986024649</v>
+        <v>0.2946273612551851</v>
       </c>
       <c r="W92">
-        <v>0.1030681334051581</v>
+        <v>0.1035487033677388</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8761794076543086</v>
+        <v>0.8665510625152502</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1500485568918237</v>
+        <v>0.1510585568918237</v>
       </c>
       <c r="C93">
-        <v>-126.3068223657695</v>
+        <v>-132.1172923354289</v>
       </c>
       <c r="D93">
-        <v>197.1221776342305</v>
+        <v>195.2307076645711</v>
       </c>
       <c r="E93">
-        <v>48.12900000000002</v>
+        <v>52.048</v>
       </c>
       <c r="F93">
-        <v>356.629</v>
+        <v>360.548</v>
       </c>
       <c r="G93">
         <v>33.2</v>
@@ -8907,37 +8907,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M93">
-        <v>52.35313720000001</v>
+        <v>52.92844640000001</v>
       </c>
       <c r="N93">
-        <v>-6.986470533333332</v>
+        <v>-7.561779733333331</v>
       </c>
       <c r="O93">
-        <v>-2.375399981333333</v>
+        <v>-2.571005109333333</v>
       </c>
       <c r="P93">
-        <v>-4.611070551999999</v>
+        <v>-4.990774623999998</v>
       </c>
       <c r="Q93">
-        <v>-0.3110705519999986</v>
+        <v>-0.6907746239999977</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6202137425242378</v>
+        <v>0.6920154603397677</v>
       </c>
       <c r="T93">
-        <v>7.486536673119669</v>
+        <v>8.42235375725963</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2946273612551851</v>
+        <v>0.291424889937194</v>
       </c>
       <c r="W93">
-        <v>0.1035487033677388</v>
+        <v>0.1040188261572199</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8665510625152502</v>
+        <v>0.8571320292270409</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1510585568918237</v>
+        <v>0.1520685568918237</v>
       </c>
       <c r="C94">
-        <v>-132.1172923354289</v>
+        <v>-137.8918084025374</v>
       </c>
       <c r="D94">
-        <v>195.2307076645711</v>
+        <v>193.3751915974626</v>
       </c>
       <c r="E94">
-        <v>52.048</v>
+        <v>55.96699999999998</v>
       </c>
       <c r="F94">
-        <v>360.548</v>
+        <v>364.467</v>
       </c>
       <c r="G94">
         <v>33.2</v>
@@ -8989,37 +8989,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M94">
-        <v>52.92844640000001</v>
+        <v>53.50375560000001</v>
       </c>
       <c r="N94">
-        <v>-7.561779733333331</v>
+        <v>-8.137088933333331</v>
       </c>
       <c r="O94">
-        <v>-2.571005109333333</v>
+        <v>-2.766610237333333</v>
       </c>
       <c r="P94">
-        <v>-4.990774623999998</v>
+        <v>-5.370478695999998</v>
       </c>
       <c r="Q94">
-        <v>-0.6907746239999977</v>
+        <v>-1.070478695999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6920154603397677</v>
+        <v>0.7843319546740203</v>
       </c>
       <c r="T94">
-        <v>8.42235375725963</v>
+        <v>9.625547151153864</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.291424889937194</v>
+        <v>0.2882912889701273</v>
       </c>
       <c r="W94">
-        <v>0.1040188261572199</v>
+        <v>0.1044788387791853</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8571320292270409</v>
+        <v>0.8479155557944922</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1520685568918237</v>
+        <v>0.1530785568918238</v>
       </c>
       <c r="C95">
-        <v>-137.8918084025374</v>
+        <v>-143.6313860573095</v>
       </c>
       <c r="D95">
-        <v>193.3751915974626</v>
+        <v>191.5546139426905</v>
       </c>
       <c r="E95">
-        <v>55.96699999999998</v>
+        <v>59.88600000000002</v>
       </c>
       <c r="F95">
-        <v>364.467</v>
+        <v>368.386</v>
       </c>
       <c r="G95">
         <v>33.2</v>
@@ -9071,37 +9071,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M95">
-        <v>53.50375560000001</v>
+        <v>54.07906480000001</v>
       </c>
       <c r="N95">
-        <v>-8.137088933333331</v>
+        <v>-8.712398133333338</v>
       </c>
       <c r="O95">
-        <v>-2.766610237333333</v>
+        <v>-2.962215365333335</v>
       </c>
       <c r="P95">
-        <v>-5.370478695999998</v>
+        <v>-5.750182768000002</v>
       </c>
       <c r="Q95">
-        <v>-1.070478695999998</v>
+        <v>-1.450182768000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7843319546740203</v>
+        <v>0.9074206137863573</v>
       </c>
       <c r="T95">
-        <v>9.625547151153864</v>
+        <v>11.22980500967951</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2882912889701273</v>
+        <v>0.2852243603640621</v>
       </c>
       <c r="W95">
-        <v>0.1044788387791853</v>
+        <v>0.1049290638985557</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8479155557944922</v>
+        <v>0.8388951775413591</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1530785568918238</v>
+        <v>0.1540885568918237</v>
       </c>
       <c r="C96">
-        <v>-143.6313860573095</v>
+        <v>-149.3370029043267</v>
       </c>
       <c r="D96">
-        <v>191.5546139426905</v>
+        <v>189.7679970956733</v>
       </c>
       <c r="E96">
-        <v>59.88600000000002</v>
+        <v>63.80500000000001</v>
       </c>
       <c r="F96">
-        <v>368.386</v>
+        <v>372.305</v>
       </c>
       <c r="G96">
         <v>33.2</v>
@@ -9153,37 +9153,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M96">
-        <v>54.07906480000001</v>
+        <v>54.654374</v>
       </c>
       <c r="N96">
-        <v>-8.712398133333338</v>
+        <v>-9.28770733333333</v>
       </c>
       <c r="O96">
-        <v>-2.962215365333335</v>
+        <v>-3.157820493333332</v>
       </c>
       <c r="P96">
-        <v>-5.750182768000002</v>
+        <v>-6.129886839999998</v>
       </c>
       <c r="Q96">
-        <v>-1.450182768000001</v>
+        <v>-1.829886839999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9074206137863573</v>
+        <v>1.079744736543629</v>
       </c>
       <c r="T96">
-        <v>11.22980500967951</v>
+        <v>13.47576601161542</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2852243603640621</v>
+        <v>0.2822219986760194</v>
       </c>
       <c r="W96">
-        <v>0.1049290638985557</v>
+        <v>0.1053698105943604</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8388951775413591</v>
+        <v>0.8300647019882923</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1540885568918237</v>
+        <v>0.1550985568918237</v>
       </c>
       <c r="C97">
-        <v>-149.3370029043267</v>
+        <v>-155.0096004129957</v>
       </c>
       <c r="D97">
-        <v>189.7679970956733</v>
+        <v>188.0143995870043</v>
       </c>
       <c r="E97">
-        <v>63.80500000000001</v>
+        <v>67.72399999999999</v>
       </c>
       <c r="F97">
-        <v>372.305</v>
+        <v>376.224</v>
       </c>
       <c r="G97">
         <v>33.2</v>
@@ -9235,37 +9235,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M97">
-        <v>54.654374</v>
+        <v>55.2296832</v>
       </c>
       <c r="N97">
-        <v>-9.28770733333333</v>
+        <v>-9.86301653333333</v>
       </c>
       <c r="O97">
-        <v>-3.157820493333332</v>
+        <v>-3.353425621333332</v>
       </c>
       <c r="P97">
-        <v>-6.129886839999998</v>
+        <v>-6.509590911999997</v>
       </c>
       <c r="Q97">
-        <v>-1.829886839999997</v>
+        <v>-2.209590911999996</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.079744736543629</v>
+        <v>1.338230920679537</v>
       </c>
       <c r="T97">
-        <v>13.47576601161542</v>
+        <v>16.84470751451928</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2822219986760194</v>
+        <v>0.2792821861898109</v>
       </c>
       <c r="W97">
-        <v>0.1053698105943604</v>
+        <v>0.1058013750673358</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8300647019882923</v>
+        <v>0.8214181946759143</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1550985568918237</v>
+        <v>0.1561085568918237</v>
       </c>
       <c r="C98">
-        <v>-155.0096004129957</v>
+        <v>-160.6500855718406</v>
       </c>
       <c r="D98">
-        <v>188.0143995870043</v>
+        <v>186.2929144281593</v>
       </c>
       <c r="E98">
-        <v>67.72399999999999</v>
+        <v>71.64299999999997</v>
       </c>
       <c r="F98">
-        <v>376.224</v>
+        <v>380.143</v>
       </c>
       <c r="G98">
         <v>33.2</v>
@@ -9317,37 +9317,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M98">
-        <v>55.2296832</v>
+        <v>55.8049924</v>
       </c>
       <c r="N98">
-        <v>-9.86301653333333</v>
+        <v>-10.43832573333333</v>
       </c>
       <c r="O98">
-        <v>-3.353425621333332</v>
+        <v>-3.549030749333332</v>
       </c>
       <c r="P98">
-        <v>-6.509590911999997</v>
+        <v>-6.889294983999998</v>
       </c>
       <c r="Q98">
-        <v>-2.209590911999996</v>
+        <v>-2.589294983999997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.338230920679534</v>
+        <v>1.769041227572712</v>
       </c>
       <c r="T98">
-        <v>16.84470751451924</v>
+        <v>22.45961001935898</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2792821861898109</v>
+        <v>0.2764029883940397</v>
       </c>
       <c r="W98">
-        <v>0.1058013750673358</v>
+        <v>0.106224041303755</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8214181946759143</v>
+        <v>0.8129499658648224</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1561085568918237</v>
+        <v>0.1571185568918237</v>
       </c>
       <c r="C99">
-        <v>-160.6500855718406</v>
+        <v>-166.2593324527384</v>
       </c>
       <c r="D99">
-        <v>186.2929144281593</v>
+        <v>184.6026675472616</v>
       </c>
       <c r="E99">
-        <v>71.64299999999997</v>
+        <v>75.56199999999995</v>
       </c>
       <c r="F99">
-        <v>380.143</v>
+        <v>384.062</v>
       </c>
       <c r="G99">
         <v>33.2</v>
@@ -9399,37 +9399,37 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M99">
-        <v>55.8049924</v>
+        <v>56.3803016</v>
       </c>
       <c r="N99">
-        <v>-10.43832573333333</v>
+        <v>-11.01363493333332</v>
       </c>
       <c r="O99">
-        <v>-3.549030749333332</v>
+        <v>-3.74463587733333</v>
       </c>
       <c r="P99">
-        <v>-6.889294983999998</v>
+        <v>-7.268999055999991</v>
       </c>
       <c r="Q99">
-        <v>-2.589294983999997</v>
+        <v>-2.968999055999991</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.769041227572712</v>
+        <v>2.630661841359067</v>
       </c>
       <c r="T99">
-        <v>22.45961001935898</v>
+        <v>33.68941502903847</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2764029883940397</v>
+        <v>0.2735825497369576</v>
       </c>
       <c r="W99">
-        <v>0.106224041303755</v>
+        <v>0.1066380816986146</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8129499658648224</v>
+        <v>0.8046545580498753</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1571185568918237</v>
+        <v>0.2166814735678335</v>
       </c>
       <c r="C100">
-        <v>-166.2593324527384</v>
+        <v>-234.5239462616098</v>
       </c>
       <c r="D100">
-        <v>184.6026675472616</v>
+        <v>120.2570537383902</v>
       </c>
       <c r="E100">
-        <v>75.56199999999995</v>
+        <v>79.48099999999999</v>
       </c>
       <c r="F100">
-        <v>384.062</v>
+        <v>387.981</v>
       </c>
       <c r="G100">
         <v>33.2</v>
@@ -9481,129 +9481,47 @@
         <v>45.36666666666667</v>
       </c>
       <c r="M100">
-        <v>56.3803016</v>
+        <v>77.9065848</v>
       </c>
       <c r="N100">
-        <v>-11.01363493333332</v>
+        <v>-32.53991813333333</v>
       </c>
       <c r="O100">
-        <v>-3.74463587733333</v>
+        <v>-11.06357216533333</v>
       </c>
       <c r="P100">
-        <v>-7.268999055999991</v>
+        <v>-21.476345968</v>
       </c>
       <c r="Q100">
-        <v>-2.968999055999991</v>
+        <v>-17.176345968</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.630661841359067</v>
+        <v>5.724815350319115</v>
       </c>
       <c r="T100">
-        <v>33.68941502903847</v>
+        <v>74.01660778611959</v>
       </c>
       <c r="U100">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.2735825497369576</v>
+        <v>0.1979892547756332</v>
       </c>
       <c r="W100">
-        <v>0.1066380816986146</v>
+        <v>0.1610437576410529</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8046545580498753</v>
+        <v>0.5823213375753916</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2166814735678335</v>
-      </c>
-      <c r="C101">
-        <v>-234.5239462616098</v>
-      </c>
-      <c r="D101">
-        <v>120.2570537383902</v>
-      </c>
-      <c r="E101">
-        <v>79.48099999999999</v>
-      </c>
-      <c r="F101">
-        <v>387.981</v>
-      </c>
-      <c r="G101">
-        <v>33.2</v>
-      </c>
-      <c r="H101">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>49.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>4.300000000000001</v>
-      </c>
-      <c r="L101">
-        <v>45.36666666666667</v>
-      </c>
-      <c r="M101">
-        <v>77.9065848</v>
-      </c>
-      <c r="N101">
-        <v>-32.53991813333333</v>
-      </c>
-      <c r="O101">
-        <v>-11.06357216533333</v>
-      </c>
-      <c r="P101">
-        <v>-21.476345968</v>
-      </c>
-      <c r="Q101">
-        <v>-17.176345968</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.724815350319115</v>
-      </c>
-      <c r="T101">
-        <v>74.01660778611959</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1979892547756332</v>
-      </c>
-      <c r="W101">
-        <v>0.1610437576410529</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5823213375753916</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
